--- a/policy.xlsx
+++ b/policy.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AF0FCC-E5E6-42E5-BF86-496CDFA0D099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7815" yWindow="3975" windowWidth="26505" windowHeight="14550" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7815" yWindow="3975" windowWidth="26505" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="추가지원금" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="43">
   <si>
     <t>모델명</t>
   </si>
@@ -970,12 +970,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>워치9 44mm</t>
-  </si>
-  <si>
-    <t>워치9 40mm</t>
-  </si>
-  <si>
     <t>S26 FE</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1045,7 +1039,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1056,9 +1050,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1278,7 +1269,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:S1004"/>
+  <dimension ref="A1:S1002"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.90234375" bestFit="1" customWidth="1"/>
@@ -1871,7 +1862,7 @@
         <v>30000</v>
       </c>
       <c r="N11" s="2">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="O11" s="2">
         <v>200000</v>
@@ -1925,7 +1916,7 @@
         <v>30000</v>
       </c>
       <c r="N12" s="2">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="O12" s="2">
         <v>200000</v>
@@ -1979,7 +1970,7 @@
         <v>30000</v>
       </c>
       <c r="N13" s="2">
-        <v>654900</v>
+        <v>250000</v>
       </c>
       <c r="O13" s="2">
         <v>400000</v>
@@ -2033,7 +2024,7 @@
         <v>30000</v>
       </c>
       <c r="N14" s="2">
-        <v>350000</v>
+        <v>250000</v>
       </c>
       <c r="O14" s="2">
         <v>250000</v>
@@ -2048,7 +2039,7 @@
     </row>
     <row r="15" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="4">
         <v>250000</v>
@@ -2375,10 +2366,10 @@
         <v>31</v>
       </c>
       <c r="B21" s="4">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="C21" s="4">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="D21" s="4">
         <v>400000</v>
@@ -2507,10 +2498,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="2">
-        <v>0</v>
+        <v>197400</v>
       </c>
       <c r="K23" s="2">
-        <v>0</v>
+        <v>197400</v>
       </c>
       <c r="L23" s="2">
         <v>0</v>
@@ -2519,10 +2510,10 @@
         <v>0</v>
       </c>
       <c r="N23" s="2">
-        <v>0</v>
+        <v>197400</v>
       </c>
       <c r="O23" s="2">
-        <v>0</v>
+        <v>197400</v>
       </c>
       <c r="P23" s="2">
         <v>0</v>
@@ -2641,57 +2632,43 @@
       <c r="S25" s="1"/>
     </row>
     <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2">
-        <v>379000</v>
-      </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2">
-        <v>325800</v>
-      </c>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
       <c r="S26" s="1"/>
     </row>
     <row r="27" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2">
-        <v>100000</v>
-      </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2">
-        <v>379000</v>
-      </c>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2">
-        <v>365000</v>
-      </c>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
       <c r="S27" s="1"/>
     </row>
     <row r="28" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2754,46 +2731,8 @@
       <c r="Q30" s="1"/>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="S31" s="1"/>
-    </row>
-    <row r="32" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="S32" s="1"/>
-    </row>
+    <row r="31" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -3764,8 +3703,6 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4752,7 +4689,7 @@
     </row>
     <row r="15" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="3">
         <v>150000</v>
@@ -7417,7 +7354,7 @@
     </row>
     <row r="15" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="3">
         <v>133000</v>
@@ -10334,7 +10271,7 @@
     </row>
     <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="3">
         <v>0</v>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="44">
   <si>
     <t>모델명</t>
   </si>
@@ -973,6 +973,15 @@
     <t>S26 FE</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>가입유형</t>
+  </si>
+  <si>
+    <t>기기변경</t>
+  </si>
+  <si>
+    <t>번호이동</t>
+  </si>
 </sst>
 </file>
 
@@ -1502,16 +1511,16 @@
         <v>23</v>
       </c>
       <c r="B5" s="4">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="D5" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="E5" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="F5" s="2">
         <v>400000</v>
@@ -1556,16 +1565,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="4">
-        <v>360000</v>
+        <v>350000</v>
       </c>
       <c r="C6" s="4">
-        <v>360000</v>
+        <v>350000</v>
       </c>
       <c r="D6" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="E6" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="F6" s="2">
         <v>300000</v>
@@ -1610,16 +1619,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="4">
-        <v>360000</v>
+        <v>350000</v>
       </c>
       <c r="C7" s="4">
-        <v>360000</v>
+        <v>350000</v>
       </c>
       <c r="D7" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="E7" s="4">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="F7" s="2">
         <v>300000</v>
@@ -1724,10 +1733,10 @@
         <v>300000</v>
       </c>
       <c r="D9" s="4">
-        <v>400000</v>
+        <v>350000</v>
       </c>
       <c r="E9" s="4">
-        <v>400000</v>
+        <v>350000</v>
       </c>
       <c r="F9" s="2">
         <v>300000</v>
@@ -2204,16 +2213,16 @@
         <v>28</v>
       </c>
       <c r="B18" s="4">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="C18" s="4">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="D18" s="4">
-        <v>400000</v>
+        <v>450000</v>
       </c>
       <c r="E18" s="4">
-        <v>380000</v>
+        <v>450000</v>
       </c>
       <c r="F18" s="2">
         <v>400000</v>
@@ -2372,10 +2381,10 @@
         <v>400000</v>
       </c>
       <c r="D21" s="4">
-        <v>400000</v>
+        <v>450000</v>
       </c>
       <c r="E21" s="4">
-        <v>380000</v>
+        <v>450000</v>
       </c>
       <c r="F21" s="2">
         <v>400000</v>
@@ -9056,171 +9065,173 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AB1002"/>
+  <dimension ref="A1:AC1005"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.90234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="23" width="8.359375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.359375" customWidth="1"/>
-    <col min="25" max="28" width="8.359375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.90234375" customWidth="1"/>
+    <col min="3" max="24" width="8.359375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.359375" customWidth="1"/>
+    <col min="26" max="29" width="8.359375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3">
+      <c r="B1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="3">
         <v>22000</v>
       </c>
-      <c r="C1" s="3">
+      <c r="D1" s="3">
         <v>28000</v>
       </c>
-      <c r="D1" s="3">
+      <c r="E1" s="3">
         <v>29000</v>
       </c>
-      <c r="E1" s="3">
+      <c r="F1" s="3">
         <v>33000</v>
       </c>
-      <c r="F1" s="3">
+      <c r="G1" s="3">
         <v>37000</v>
       </c>
-      <c r="G1" s="3">
+      <c r="H1" s="3">
         <v>39000</v>
       </c>
-      <c r="H1" s="3">
+      <c r="I1" s="3">
         <v>43000</v>
       </c>
-      <c r="I1" s="3">
+      <c r="J1" s="3">
         <v>44000</v>
       </c>
-      <c r="J1" s="3">
+      <c r="K1" s="3">
         <v>45000</v>
       </c>
-      <c r="K1" s="3">
+      <c r="L1" s="3">
         <v>47000</v>
       </c>
-      <c r="L1" s="3">
+      <c r="M1" s="3">
         <v>49000</v>
       </c>
-      <c r="M1" s="3">
+      <c r="N1" s="3">
         <v>55000</v>
       </c>
-      <c r="N1" s="3">
+      <c r="O1" s="3">
         <v>59000</v>
       </c>
-      <c r="O1" s="3">
+      <c r="P1" s="3">
         <v>61000</v>
       </c>
-      <c r="P1" s="3">
+      <c r="Q1" s="3">
         <v>63000</v>
       </c>
-      <c r="Q1" s="3">
+      <c r="R1" s="3">
         <v>66000</v>
       </c>
-      <c r="R1" s="3">
+      <c r="S1" s="3">
         <v>68000</v>
       </c>
-      <c r="S1" s="3">
+      <c r="T1" s="3">
         <v>69000</v>
       </c>
-      <c r="T1" s="3">
+      <c r="U1" s="3">
         <v>70000</v>
       </c>
-      <c r="U1" s="3">
+      <c r="V1" s="3">
         <v>75000</v>
       </c>
-      <c r="V1" s="3">
+      <c r="W1" s="3">
         <v>78000</v>
       </c>
-      <c r="W1" s="3">
+      <c r="X1" s="3">
         <v>85000</v>
       </c>
-      <c r="X1" s="3">
+      <c r="Y1" s="3">
         <v>88000</v>
       </c>
-      <c r="Y1" s="3">
+      <c r="Z1" s="3">
         <v>95000</v>
       </c>
-      <c r="Z1" s="3">
+      <c r="AA1" s="3">
         <v>105000</v>
       </c>
-      <c r="AA1" s="3">
+      <c r="AB1" s="3">
         <v>115000</v>
       </c>
-      <c r="AB1" s="3">
+      <c r="AC1" s="3">
         <v>130000</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="3">
-        <v>0</v>
-      </c>
+      <c r="B2" s="4"/>
       <c r="C2" s="3">
         <v>0</v>
       </c>
       <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
         <v>175000</v>
       </c>
-      <c r="E2" s="3">
+      <c r="F2" s="3">
         <v>198000</v>
       </c>
-      <c r="F2" s="3">
+      <c r="G2" s="3">
         <v>222000</v>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="3">
         <v>233000</v>
       </c>
-      <c r="H2" s="3">
+      <c r="I2" s="3">
         <v>257000</v>
       </c>
-      <c r="I2" s="3">
+      <c r="J2" s="3">
         <v>262000</v>
       </c>
-      <c r="J2" s="3">
+      <c r="K2" s="3">
         <v>268000</v>
       </c>
-      <c r="K2" s="3">
+      <c r="L2" s="3">
         <v>280000</v>
       </c>
-      <c r="L2" s="3">
+      <c r="M2" s="3">
         <v>291000</v>
       </c>
-      <c r="M2" s="3">
+      <c r="N2" s="3">
         <v>326000</v>
       </c>
-      <c r="N2" s="3">
+      <c r="O2" s="3">
         <v>350000</v>
       </c>
-      <c r="O2" s="3">
+      <c r="P2" s="3">
         <v>361000</v>
       </c>
-      <c r="P2" s="3">
+      <c r="Q2" s="3">
         <v>373000</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="R2" s="3">
         <v>390000</v>
       </c>
-      <c r="R2" s="3">
+      <c r="S2" s="3">
         <v>402000</v>
       </c>
-      <c r="S2" s="3">
+      <c r="T2" s="3">
         <v>407000</v>
       </c>
-      <c r="T2" s="3">
+      <c r="U2" s="3">
         <v>414000</v>
       </c>
-      <c r="U2" s="3">
+      <c r="V2" s="3">
         <v>442000</v>
       </c>
-      <c r="V2" s="3">
+      <c r="W2" s="3">
         <v>460000</v>
       </c>
-      <c r="W2" s="3">
-        <v>500000</v>
-      </c>
       <c r="X2" s="3">
         <v>500000</v>
       </c>
@@ -9236,77 +9247,78 @@
       <c r="AB2" s="3">
         <v>500000</v>
       </c>
+      <c r="AC2" s="3">
+        <v>500000</v>
+      </c>
     </row>
-    <row r="3" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="3">
-        <v>0</v>
-      </c>
+      <c r="B3" s="4"/>
       <c r="C3" s="3">
         <v>0</v>
       </c>
       <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
         <v>175000</v>
       </c>
-      <c r="E3" s="3">
+      <c r="F3" s="3">
         <v>198000</v>
       </c>
-      <c r="F3" s="3">
+      <c r="G3" s="3">
         <v>222000</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="3">
         <v>233000</v>
       </c>
-      <c r="H3" s="3">
+      <c r="I3" s="3">
         <v>257000</v>
       </c>
-      <c r="I3" s="3">
+      <c r="J3" s="3">
         <v>262000</v>
       </c>
-      <c r="J3" s="3">
+      <c r="K3" s="3">
         <v>268000</v>
       </c>
-      <c r="K3" s="3">
+      <c r="L3" s="3">
         <v>280000</v>
       </c>
-      <c r="L3" s="3">
+      <c r="M3" s="3">
         <v>291000</v>
       </c>
-      <c r="M3" s="3">
+      <c r="N3" s="3">
         <v>326000</v>
       </c>
-      <c r="N3" s="3">
+      <c r="O3" s="3">
         <v>350000</v>
       </c>
-      <c r="O3" s="3">
+      <c r="P3" s="3">
         <v>361000</v>
       </c>
-      <c r="P3" s="3">
+      <c r="Q3" s="3">
         <v>373000</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="R3" s="3">
         <v>390000</v>
       </c>
-      <c r="R3" s="3">
+      <c r="S3" s="3">
         <v>402000</v>
       </c>
-      <c r="S3" s="3">
+      <c r="T3" s="3">
         <v>407000</v>
       </c>
-      <c r="T3" s="3">
+      <c r="U3" s="3">
         <v>414000</v>
       </c>
-      <c r="U3" s="3">
+      <c r="V3" s="3">
         <v>442000</v>
       </c>
-      <c r="V3" s="3">
+      <c r="W3" s="3">
         <v>460000</v>
       </c>
-      <c r="W3" s="3">
-        <v>500000</v>
-      </c>
       <c r="X3" s="3">
         <v>500000</v>
       </c>
@@ -9322,77 +9334,78 @@
       <c r="AB3" s="3">
         <v>500000</v>
       </c>
+      <c r="AC3" s="3">
+        <v>500000</v>
+      </c>
     </row>
-    <row r="4" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="3">
-        <v>0</v>
-      </c>
+      <c r="B4" s="4"/>
       <c r="C4" s="3">
         <v>0</v>
       </c>
       <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
         <v>175000</v>
       </c>
-      <c r="E4" s="3">
+      <c r="F4" s="3">
         <v>198000</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <v>222000</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>233000</v>
       </c>
-      <c r="H4" s="3">
+      <c r="I4" s="3">
         <v>257000</v>
       </c>
-      <c r="I4" s="3">
+      <c r="J4" s="3">
         <v>262000</v>
       </c>
-      <c r="J4" s="3">
+      <c r="K4" s="3">
         <v>268000</v>
       </c>
-      <c r="K4" s="3">
+      <c r="L4" s="3">
         <v>280000</v>
       </c>
-      <c r="L4" s="3">
+      <c r="M4" s="3">
         <v>291000</v>
       </c>
-      <c r="M4" s="3">
+      <c r="N4" s="3">
         <v>326000</v>
       </c>
-      <c r="N4" s="3">
+      <c r="O4" s="3">
         <v>350000</v>
       </c>
-      <c r="O4" s="3">
+      <c r="P4" s="3">
         <v>361000</v>
       </c>
-      <c r="P4" s="3">
+      <c r="Q4" s="3">
         <v>373000</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="R4" s="3">
         <v>390000</v>
       </c>
-      <c r="R4" s="3">
+      <c r="S4" s="3">
         <v>402000</v>
       </c>
-      <c r="S4" s="3">
+      <c r="T4" s="3">
         <v>407000</v>
       </c>
-      <c r="T4" s="3">
+      <c r="U4" s="3">
         <v>414000</v>
       </c>
-      <c r="U4" s="3">
+      <c r="V4" s="3">
         <v>442000</v>
       </c>
-      <c r="V4" s="3">
+      <c r="W4" s="3">
         <v>460000</v>
       </c>
-      <c r="W4" s="3">
-        <v>500000</v>
-      </c>
       <c r="X4" s="3">
         <v>500000</v>
       </c>
@@ -9408,76 +9421,77 @@
       <c r="AB4" s="3">
         <v>500000</v>
       </c>
+      <c r="AC4" s="3">
+        <v>500000</v>
+      </c>
     </row>
-    <row r="5" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="3">
-        <v>0</v>
-      </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="3">
         <v>0</v>
       </c>
       <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
         <v>175000</v>
       </c>
-      <c r="E5" s="3">
+      <c r="F5" s="3">
         <v>198000</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <v>222000</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>233000</v>
       </c>
-      <c r="H5" s="3">
+      <c r="I5" s="3">
         <v>257000</v>
       </c>
-      <c r="I5" s="3">
+      <c r="J5" s="3">
         <v>262000</v>
       </c>
-      <c r="J5" s="3">
+      <c r="K5" s="3">
         <v>268000</v>
       </c>
-      <c r="K5" s="3">
+      <c r="L5" s="3">
         <v>280000</v>
       </c>
-      <c r="L5" s="3">
+      <c r="M5" s="3">
         <v>291000</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>326000</v>
       </c>
-      <c r="N5" s="3">
+      <c r="O5" s="3">
         <v>350000</v>
       </c>
-      <c r="O5" s="3">
+      <c r="P5" s="3">
         <v>361000</v>
       </c>
-      <c r="P5" s="3">
+      <c r="Q5" s="3">
         <v>373000</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="R5" s="3">
         <v>390000</v>
       </c>
-      <c r="R5" s="3">
+      <c r="S5" s="3">
         <v>402000</v>
       </c>
-      <c r="S5" s="3">
+      <c r="T5" s="3">
         <v>407000</v>
       </c>
-      <c r="T5" s="3">
+      <c r="U5" s="3">
         <v>414000</v>
       </c>
-      <c r="U5" s="3">
+      <c r="V5" s="3">
         <v>442000</v>
       </c>
-      <c r="V5" s="3">
+      <c r="W5" s="3">
         <v>460000</v>
-      </c>
-      <c r="W5" s="3">
-        <v>600000</v>
       </c>
       <c r="X5" s="3">
         <v>600000</v>
@@ -9494,76 +9508,77 @@
       <c r="AB5" s="3">
         <v>600000</v>
       </c>
+      <c r="AC5" s="3">
+        <v>600000</v>
+      </c>
     </row>
-    <row r="6" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="3">
-        <v>0</v>
-      </c>
+      <c r="B6" s="2"/>
       <c r="C6" s="3">
         <v>0</v>
       </c>
       <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
         <v>175000</v>
       </c>
-      <c r="E6" s="3">
+      <c r="F6" s="3">
         <v>198000</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>222000</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>233000</v>
       </c>
-      <c r="H6" s="3">
+      <c r="I6" s="3">
         <v>257000</v>
       </c>
-      <c r="I6" s="3">
+      <c r="J6" s="3">
         <v>262000</v>
       </c>
-      <c r="J6" s="3">
+      <c r="K6" s="3">
         <v>268000</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="3">
         <v>280000</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M6" s="3">
         <v>291000</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>326000</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="3">
         <v>350000</v>
       </c>
-      <c r="O6" s="3">
+      <c r="P6" s="3">
         <v>361000</v>
       </c>
-      <c r="P6" s="3">
+      <c r="Q6" s="3">
         <v>373000</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="R6" s="3">
         <v>390000</v>
       </c>
-      <c r="R6" s="3">
+      <c r="S6" s="3">
         <v>402000</v>
       </c>
-      <c r="S6" s="3">
+      <c r="T6" s="3">
         <v>407000</v>
       </c>
-      <c r="T6" s="3">
+      <c r="U6" s="3">
         <v>414000</v>
       </c>
-      <c r="U6" s="3">
+      <c r="V6" s="3">
         <v>442000</v>
       </c>
-      <c r="V6" s="3">
+      <c r="W6" s="3">
         <v>460000</v>
-      </c>
-      <c r="W6" s="3">
-        <v>600000</v>
       </c>
       <c r="X6" s="3">
         <v>600000</v>
@@ -9580,76 +9595,77 @@
       <c r="AB6" s="3">
         <v>600000</v>
       </c>
+      <c r="AC6" s="3">
+        <v>600000</v>
+      </c>
     </row>
-    <row r="7" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="3">
-        <v>0</v>
-      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="3">
         <v>0</v>
       </c>
       <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
         <v>175000</v>
       </c>
-      <c r="E7" s="3">
+      <c r="F7" s="3">
         <v>198000</v>
       </c>
-      <c r="F7" s="3">
+      <c r="G7" s="3">
         <v>222000</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>233000</v>
       </c>
-      <c r="H7" s="3">
+      <c r="I7" s="3">
         <v>257000</v>
       </c>
-      <c r="I7" s="3">
+      <c r="J7" s="3">
         <v>262000</v>
       </c>
-      <c r="J7" s="3">
+      <c r="K7" s="3">
         <v>268000</v>
       </c>
-      <c r="K7" s="3">
+      <c r="L7" s="3">
         <v>280000</v>
       </c>
-      <c r="L7" s="3">
+      <c r="M7" s="3">
         <v>291000</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>326000</v>
       </c>
-      <c r="N7" s="3">
+      <c r="O7" s="3">
         <v>350000</v>
       </c>
-      <c r="O7" s="3">
+      <c r="P7" s="3">
         <v>361000</v>
       </c>
-      <c r="P7" s="3">
+      <c r="Q7" s="3">
         <v>373000</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="R7" s="3">
         <v>390000</v>
       </c>
-      <c r="R7" s="3">
+      <c r="S7" s="3">
         <v>402000</v>
       </c>
-      <c r="S7" s="3">
+      <c r="T7" s="3">
         <v>407000</v>
       </c>
-      <c r="T7" s="3">
+      <c r="U7" s="3">
         <v>414000</v>
       </c>
-      <c r="U7" s="3">
+      <c r="V7" s="3">
         <v>442000</v>
       </c>
-      <c r="V7" s="3">
+      <c r="W7" s="3">
         <v>460000</v>
-      </c>
-      <c r="W7" s="3">
-        <v>600000</v>
       </c>
       <c r="X7" s="3">
         <v>600000</v>
@@ -9666,76 +9682,79 @@
       <c r="AB7" s="3">
         <v>600000</v>
       </c>
+      <c r="AC7" s="3">
+        <v>600000</v>
+      </c>
     </row>
-    <row r="8" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3">
-        <v>0</v>
+      <c r="B8" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="C8" s="3">
         <v>0</v>
       </c>
       <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
         <v>175000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>198000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>222000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>233000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>257000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>262000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>268000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>280000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>291000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>326000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>350000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>361000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>373000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>390000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>402000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>407000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>414000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>442000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>460000</v>
-      </c>
-      <c r="W8" s="3">
-        <v>600000</v>
       </c>
       <c r="X8" s="3">
         <v>600000</v>
@@ -9752,162 +9771,168 @@
       <c r="AB8" s="3">
         <v>600000</v>
       </c>
+      <c r="AC8" s="3">
+        <v>600000</v>
+      </c>
     </row>
-    <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="3">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="C9" s="3">
         <v>0</v>
       </c>
       <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
         <v>175000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>198000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>222000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>233000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>257000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>262000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>268000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>280000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>291000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>326000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>350000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>361000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>373000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>390000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>402000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>407000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>414000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>442000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>460000</v>
       </c>
-      <c r="W9" s="3">
-        <v>600000</v>
-      </c>
       <c r="X9" s="3">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="Y9" s="3">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="Z9" s="3">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="AA9" s="3">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="AB9" s="3">
-        <v>600000</v>
+        <v>500000</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="3">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="C10" s="3">
         <v>0</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
         <v>175000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>198000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>222000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>233000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>257000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>262000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>268000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>280000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>291000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>326000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>350000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>361000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>373000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>390000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>402000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>407000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>414000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>442000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>460000</v>
-      </c>
-      <c r="W10" s="3">
-        <v>600000</v>
       </c>
       <c r="X10" s="3">
         <v>600000</v>
@@ -9924,77 +9949,80 @@
       <c r="AB10" s="3">
         <v>600000</v>
       </c>
+      <c r="AC10" s="3">
+        <v>600000</v>
+      </c>
     </row>
-    <row r="11" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="3">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="C11" s="3">
         <v>0</v>
       </c>
       <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
         <v>175000</v>
       </c>
-      <c r="E11" s="3">
+      <c r="F11" s="3">
         <v>198000</v>
       </c>
-      <c r="F11" s="3">
+      <c r="G11" s="3">
         <v>222000</v>
       </c>
-      <c r="G11" s="3">
+      <c r="H11" s="3">
         <v>233000</v>
       </c>
-      <c r="H11" s="3">
+      <c r="I11" s="3">
         <v>257000</v>
       </c>
-      <c r="I11" s="3">
+      <c r="J11" s="3">
         <v>262000</v>
       </c>
-      <c r="J11" s="3">
+      <c r="K11" s="3">
         <v>268000</v>
       </c>
-      <c r="K11" s="3">
+      <c r="L11" s="3">
         <v>280000</v>
       </c>
-      <c r="L11" s="3">
+      <c r="M11" s="3">
         <v>291000</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="3">
         <v>326000</v>
       </c>
-      <c r="N11" s="3">
+      <c r="O11" s="3">
         <v>350000</v>
       </c>
-      <c r="O11" s="3">
+      <c r="P11" s="3">
         <v>361000</v>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3">
         <v>373000</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="R11" s="3">
         <v>390000</v>
       </c>
-      <c r="R11" s="3">
+      <c r="S11" s="3">
         <v>402000</v>
       </c>
-      <c r="S11" s="3">
+      <c r="T11" s="3">
         <v>407000</v>
       </c>
-      <c r="T11" s="3">
+      <c r="U11" s="3">
         <v>414000</v>
       </c>
-      <c r="U11" s="3">
+      <c r="V11" s="3">
         <v>442000</v>
       </c>
-      <c r="V11" s="3">
+      <c r="W11" s="3">
         <v>460000</v>
       </c>
-      <c r="W11" s="3">
-        <v>500000</v>
-      </c>
       <c r="X11" s="3">
         <v>500000</v>
       </c>
@@ -10010,163 +10038,169 @@
       <c r="AB11" s="3">
         <v>500000</v>
       </c>
+      <c r="AC11" s="3">
+        <v>500000</v>
+      </c>
     </row>
-    <row r="12" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="3">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="C12" s="3">
         <v>0</v>
       </c>
       <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
         <v>175000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>198000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>222000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>233000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>257000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>262000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>268000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>280000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>291000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>326000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>350000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>361000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>373000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>390000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>402000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>407000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>414000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>442000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>460000</v>
       </c>
-      <c r="W12" s="3">
-        <v>500000</v>
-      </c>
       <c r="X12" s="3">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="Y12" s="3">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="Z12" s="3">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="AA12" s="3">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="AB12" s="3">
-        <v>500000</v>
+        <v>600000</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>600000</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="3">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="C13" s="3">
         <v>0</v>
       </c>
       <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
         <v>175000</v>
       </c>
-      <c r="E13" s="3">
+      <c r="F13" s="3">
         <v>198000</v>
       </c>
-      <c r="F13" s="3">
+      <c r="G13" s="3">
         <v>222000</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H13" s="3">
         <v>233000</v>
       </c>
-      <c r="H13" s="3">
+      <c r="I13" s="3">
         <v>257000</v>
       </c>
-      <c r="I13" s="3">
+      <c r="J13" s="3">
         <v>262000</v>
       </c>
-      <c r="J13" s="3">
+      <c r="K13" s="3">
         <v>268000</v>
       </c>
-      <c r="K13" s="3">
+      <c r="L13" s="3">
         <v>280000</v>
       </c>
-      <c r="L13" s="3">
+      <c r="M13" s="3">
         <v>291000</v>
       </c>
-      <c r="M13" s="3">
+      <c r="N13" s="3">
         <v>326000</v>
       </c>
-      <c r="N13" s="3">
+      <c r="O13" s="3">
         <v>350000</v>
       </c>
-      <c r="O13" s="3">
+      <c r="P13" s="3">
         <v>361000</v>
       </c>
-      <c r="P13" s="3">
+      <c r="Q13" s="3">
         <v>373000</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="R13" s="3">
         <v>390000</v>
       </c>
-      <c r="R13" s="3">
+      <c r="S13" s="3">
         <v>402000</v>
       </c>
-      <c r="S13" s="3">
+      <c r="T13" s="3">
         <v>407000</v>
       </c>
-      <c r="T13" s="3">
+      <c r="U13" s="3">
         <v>414000</v>
       </c>
-      <c r="U13" s="3">
+      <c r="V13" s="3">
         <v>442000</v>
       </c>
-      <c r="V13" s="3">
+      <c r="W13" s="3">
         <v>460000</v>
       </c>
-      <c r="W13" s="3">
-        <v>500000</v>
-      </c>
       <c r="X13" s="3">
         <v>500000</v>
       </c>
@@ -10182,163 +10216,165 @@
       <c r="AB13" s="3">
         <v>500000</v>
       </c>
+      <c r="AC13" s="3">
+        <v>500000</v>
+      </c>
     </row>
-    <row r="14" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="3">
-        <v>0</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B14" s="2"/>
       <c r="C14" s="3">
         <v>0</v>
       </c>
       <c r="D14" s="3">
-        <v>239000</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>272000</v>
+        <v>175000</v>
       </c>
       <c r="F14" s="3">
-        <v>305000</v>
+        <v>198000</v>
       </c>
       <c r="G14" s="3">
-        <v>322000</v>
+        <v>222000</v>
       </c>
       <c r="H14" s="3">
-        <v>355000</v>
+        <v>233000</v>
       </c>
       <c r="I14" s="3">
-        <v>363000</v>
+        <v>257000</v>
       </c>
       <c r="J14" s="3">
-        <v>371000</v>
+        <v>262000</v>
       </c>
       <c r="K14" s="3">
-        <v>388000</v>
+        <v>268000</v>
       </c>
       <c r="L14" s="3">
-        <v>404000</v>
+        <v>280000</v>
       </c>
       <c r="M14" s="3">
-        <v>454000</v>
+        <v>291000</v>
       </c>
       <c r="N14" s="3">
-        <v>487000</v>
+        <v>326000</v>
       </c>
       <c r="O14" s="3">
-        <v>503000</v>
+        <v>350000</v>
       </c>
       <c r="P14" s="3">
-        <v>519000</v>
+        <v>361000</v>
       </c>
       <c r="Q14" s="3">
-        <v>544000</v>
+        <v>373000</v>
       </c>
       <c r="R14" s="3">
-        <v>560000</v>
+        <v>390000</v>
       </c>
       <c r="S14" s="3">
-        <v>569000</v>
+        <v>402000</v>
       </c>
       <c r="T14" s="3">
-        <v>577000</v>
+        <v>407000</v>
       </c>
       <c r="U14" s="3">
-        <v>618000</v>
+        <v>414000</v>
       </c>
       <c r="V14" s="3">
-        <v>700000</v>
+        <v>442000</v>
       </c>
       <c r="W14" s="3">
-        <v>700000</v>
+        <v>460000</v>
       </c>
       <c r="X14" s="3">
-        <v>700000</v>
+        <v>500000</v>
       </c>
       <c r="Y14" s="3">
-        <v>700000</v>
+        <v>500000</v>
       </c>
       <c r="Z14" s="3">
-        <v>700000</v>
+        <v>500000</v>
       </c>
       <c r="AA14" s="3">
-        <v>700000</v>
+        <v>500000</v>
       </c>
       <c r="AB14" s="3">
-        <v>700000</v>
+        <v>500000</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>500000</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="3">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B15" s="2"/>
       <c r="C15" s="3">
         <v>0</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>175000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>198000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>222000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>233000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>257000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>262000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>268000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>280000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>291000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>326000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>350000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>361000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>373000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>390000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>402000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>407000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>414000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>442000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>460000</v>
       </c>
-      <c r="W15" s="3">
-        <v>500000</v>
-      </c>
       <c r="X15" s="3">
         <v>500000</v>
       </c>
@@ -10354,77 +10390,78 @@
       <c r="AB15" s="3">
         <v>500000</v>
       </c>
+      <c r="AC15" s="3">
+        <v>500000</v>
+      </c>
     </row>
-    <row r="16" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="3">
-        <v>0</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B16" s="2"/>
       <c r="C16" s="3">
         <v>0</v>
       </c>
       <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
         <v>175000</v>
       </c>
-      <c r="E16" s="3">
+      <c r="F16" s="3">
         <v>198000</v>
       </c>
-      <c r="F16" s="3">
+      <c r="G16" s="3">
         <v>222000</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>233000</v>
       </c>
-      <c r="H16" s="3">
+      <c r="I16" s="3">
         <v>257000</v>
       </c>
-      <c r="I16" s="3">
+      <c r="J16" s="3">
         <v>262000</v>
       </c>
-      <c r="J16" s="3">
+      <c r="K16" s="3">
         <v>268000</v>
       </c>
-      <c r="K16" s="3">
+      <c r="L16" s="3">
         <v>280000</v>
       </c>
-      <c r="L16" s="3">
+      <c r="M16" s="3">
         <v>291000</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="3">
         <v>326000</v>
       </c>
-      <c r="N16" s="3">
+      <c r="O16" s="3">
         <v>350000</v>
       </c>
-      <c r="O16" s="3">
+      <c r="P16" s="3">
         <v>361000</v>
       </c>
-      <c r="P16" s="3">
+      <c r="Q16" s="3">
         <v>373000</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="R16" s="3">
         <v>390000</v>
       </c>
-      <c r="R16" s="3">
+      <c r="S16" s="3">
         <v>402000</v>
       </c>
-      <c r="S16" s="3">
+      <c r="T16" s="3">
         <v>407000</v>
       </c>
-      <c r="T16" s="3">
+      <c r="U16" s="3">
         <v>414000</v>
       </c>
-      <c r="U16" s="3">
+      <c r="V16" s="3">
         <v>442000</v>
       </c>
-      <c r="V16" s="3">
+      <c r="W16" s="3">
         <v>460000</v>
       </c>
-      <c r="W16" s="3">
-        <v>500000</v>
-      </c>
       <c r="X16" s="3">
         <v>500000</v>
       </c>
@@ -10440,163 +10477,165 @@
       <c r="AB16" s="3">
         <v>500000</v>
       </c>
+      <c r="AC16" s="3">
+        <v>500000</v>
+      </c>
     </row>
-    <row r="17" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="3">
-        <v>0</v>
-      </c>
+    <row r="17" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="2"/>
       <c r="C17" s="3">
         <v>0</v>
       </c>
       <c r="D17" s="3">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="E17" s="3">
-        <v>198000</v>
+        <v>239000</v>
       </c>
       <c r="F17" s="3">
-        <v>222000</v>
+        <v>272000</v>
       </c>
       <c r="G17" s="3">
-        <v>233000</v>
+        <v>305000</v>
       </c>
       <c r="H17" s="3">
-        <v>257000</v>
+        <v>322000</v>
       </c>
       <c r="I17" s="3">
-        <v>262000</v>
+        <v>355000</v>
       </c>
       <c r="J17" s="3">
-        <v>268000</v>
+        <v>363000</v>
       </c>
       <c r="K17" s="3">
-        <v>280000</v>
+        <v>371000</v>
       </c>
       <c r="L17" s="3">
-        <v>291000</v>
+        <v>388000</v>
       </c>
       <c r="M17" s="3">
-        <v>326000</v>
+        <v>404000</v>
       </c>
       <c r="N17" s="3">
-        <v>350000</v>
+        <v>454000</v>
       </c>
       <c r="O17" s="3">
-        <v>361000</v>
+        <v>487000</v>
       </c>
       <c r="P17" s="3">
-        <v>373000</v>
+        <v>503000</v>
       </c>
       <c r="Q17" s="3">
-        <v>390000</v>
+        <v>519000</v>
       </c>
       <c r="R17" s="3">
-        <v>402000</v>
+        <v>544000</v>
       </c>
       <c r="S17" s="3">
-        <v>407000</v>
+        <v>560000</v>
       </c>
       <c r="T17" s="3">
-        <v>414000</v>
+        <v>569000</v>
       </c>
       <c r="U17" s="3">
-        <v>442000</v>
+        <v>577000</v>
       </c>
       <c r="V17" s="3">
-        <v>460000</v>
+        <v>618000</v>
       </c>
       <c r="W17" s="3">
-        <v>500000</v>
+        <v>700000</v>
       </c>
       <c r="X17" s="3">
-        <v>500000</v>
+        <v>700000</v>
       </c>
       <c r="Y17" s="3">
-        <v>500000</v>
+        <v>700000</v>
       </c>
       <c r="Z17" s="3">
-        <v>500000</v>
+        <v>700000</v>
       </c>
       <c r="AA17" s="3">
-        <v>500000</v>
+        <v>700000</v>
       </c>
       <c r="AB17" s="3">
-        <v>500000</v>
+        <v>700000</v>
+      </c>
+      <c r="AC17" s="3">
+        <v>700000</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="3">
-        <v>0</v>
-      </c>
+    <row r="18" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="2"/>
       <c r="C18" s="3">
         <v>0</v>
       </c>
       <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
         <v>175000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>198000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>222000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>233000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>257000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>262000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>268000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>280000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>291000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>326000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>350000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>361000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>373000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>390000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>402000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>407000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>414000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>442000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>460000</v>
       </c>
-      <c r="W18" s="3">
-        <v>500000</v>
-      </c>
       <c r="X18" s="3">
         <v>500000</v>
       </c>
@@ -10612,77 +10651,78 @@
       <c r="AB18" s="3">
         <v>500000</v>
       </c>
+      <c r="AC18" s="3">
+        <v>500000</v>
+      </c>
     </row>
-    <row r="19" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="3">
-        <v>0</v>
-      </c>
+    <row r="19" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="2"/>
       <c r="C19" s="3">
         <v>0</v>
       </c>
       <c r="D19" s="3">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3">
         <v>175000</v>
       </c>
-      <c r="E19" s="3">
+      <c r="F19" s="3">
         <v>198000</v>
       </c>
-      <c r="F19" s="3">
+      <c r="G19" s="3">
         <v>222000</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>233000</v>
       </c>
-      <c r="H19" s="3">
+      <c r="I19" s="3">
         <v>257000</v>
       </c>
-      <c r="I19" s="3">
+      <c r="J19" s="3">
         <v>262000</v>
       </c>
-      <c r="J19" s="3">
+      <c r="K19" s="3">
         <v>268000</v>
       </c>
-      <c r="K19" s="3">
+      <c r="L19" s="3">
         <v>280000</v>
       </c>
-      <c r="L19" s="3">
+      <c r="M19" s="3">
         <v>291000</v>
       </c>
-      <c r="M19" s="3">
+      <c r="N19" s="3">
         <v>326000</v>
       </c>
-      <c r="N19" s="3">
+      <c r="O19" s="3">
         <v>350000</v>
       </c>
-      <c r="O19" s="3">
+      <c r="P19" s="3">
         <v>361000</v>
       </c>
-      <c r="P19" s="3">
+      <c r="Q19" s="3">
         <v>373000</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="R19" s="3">
         <v>390000</v>
       </c>
-      <c r="R19" s="3">
+      <c r="S19" s="3">
         <v>402000</v>
       </c>
-      <c r="S19" s="3">
+      <c r="T19" s="3">
         <v>407000</v>
       </c>
-      <c r="T19" s="3">
+      <c r="U19" s="3">
         <v>414000</v>
       </c>
-      <c r="U19" s="3">
+      <c r="V19" s="3">
         <v>442000</v>
       </c>
-      <c r="V19" s="3">
+      <c r="W19" s="3">
         <v>460000</v>
       </c>
-      <c r="W19" s="3">
-        <v>500000</v>
-      </c>
       <c r="X19" s="3">
         <v>500000</v>
       </c>
@@ -10698,77 +10738,78 @@
       <c r="AB19" s="3">
         <v>500000</v>
       </c>
+      <c r="AC19" s="3">
+        <v>500000</v>
+      </c>
     </row>
-    <row r="20" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="3">
-        <v>0</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B20" s="4"/>
       <c r="C20" s="3">
         <v>0</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>175000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>198000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>222000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>233000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>257000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>262000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>268000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>280000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>291000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>326000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>350000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>361000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>373000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>390000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>402000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>407000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>414000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>442000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>460000</v>
       </c>
-      <c r="W20" s="3">
-        <v>500000</v>
-      </c>
       <c r="X20" s="3">
         <v>500000</v>
       </c>
@@ -10784,77 +10825,78 @@
       <c r="AB20" s="3">
         <v>500000</v>
       </c>
+      <c r="AC20" s="3">
+        <v>500000</v>
+      </c>
     </row>
-    <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="3">
-        <v>0</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B21" s="4"/>
       <c r="C21" s="3">
         <v>0</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>175000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>198000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>222000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>233000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>257000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>262000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>268000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>280000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>291000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>326000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>350000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>361000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>373000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>390000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>402000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>407000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>414000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>442000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>460000</v>
       </c>
-      <c r="W21" s="3">
-        <v>500000</v>
-      </c>
       <c r="X21" s="3">
         <v>500000</v>
       </c>
@@ -10870,77 +10912,78 @@
       <c r="AB21" s="3">
         <v>500000</v>
       </c>
+      <c r="AC21" s="3">
+        <v>500000</v>
+      </c>
     </row>
-    <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="3">
-        <v>0</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B22" s="4"/>
       <c r="C22" s="3">
         <v>0</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
         <v>175000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>198000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>222000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>233000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>257000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>262000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>268000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>280000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>291000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>326000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>350000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>361000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>373000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>390000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>402000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>407000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>414000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>442000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>460000</v>
       </c>
-      <c r="W22" s="3">
-        <v>500000</v>
-      </c>
       <c r="X22" s="3">
         <v>500000</v>
       </c>
@@ -10956,272 +10999,536 @@
       <c r="AB22" s="3">
         <v>500000</v>
       </c>
+      <c r="AC22" s="3">
+        <v>500000</v>
+      </c>
     </row>
-    <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="3">
-        <v>0</v>
-      </c>
+    <row r="23" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="4"/>
       <c r="C23" s="3">
         <v>0</v>
       </c>
       <c r="D23" s="3">
-        <v>158000</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3">
-        <v>180000</v>
+        <v>175000</v>
       </c>
       <c r="F23" s="3">
-        <v>202000</v>
+        <v>198000</v>
       </c>
       <c r="G23" s="3">
-        <v>213000</v>
+        <v>222000</v>
       </c>
       <c r="H23" s="3">
-        <v>235000</v>
+        <v>233000</v>
       </c>
       <c r="I23" s="3">
-        <v>240000</v>
+        <v>257000</v>
       </c>
       <c r="J23" s="3">
-        <v>245000</v>
+        <v>262000</v>
       </c>
       <c r="K23" s="3">
-        <v>257000</v>
+        <v>268000</v>
       </c>
       <c r="L23" s="3">
-        <v>267000</v>
+        <v>280000</v>
       </c>
       <c r="M23" s="3">
-        <v>300000</v>
+        <v>291000</v>
       </c>
       <c r="N23" s="3">
-        <v>311000</v>
+        <v>326000</v>
       </c>
       <c r="O23" s="3">
-        <v>321000</v>
+        <v>350000</v>
       </c>
       <c r="P23" s="3">
-        <v>332000</v>
+        <v>361000</v>
       </c>
       <c r="Q23" s="3">
-        <v>348000</v>
+        <v>373000</v>
       </c>
       <c r="R23" s="3">
-        <v>358000</v>
+        <v>390000</v>
       </c>
       <c r="S23" s="3">
-        <v>363000</v>
+        <v>402000</v>
       </c>
       <c r="T23" s="3">
-        <v>369000</v>
+        <v>407000</v>
       </c>
       <c r="U23" s="3">
-        <v>395000</v>
+        <v>414000</v>
       </c>
       <c r="V23" s="3">
-        <v>395000</v>
+        <v>442000</v>
       </c>
       <c r="W23" s="3">
-        <v>400000</v>
+        <v>460000</v>
       </c>
       <c r="X23" s="3">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="Y23" s="3">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="Z23" s="3">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="AA23" s="3">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="AB23" s="3">
-        <v>400000</v>
+        <v>500000</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>500000</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="3">
-        <v>0</v>
-      </c>
+    <row r="24" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="4"/>
       <c r="C24" s="3">
         <v>0</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>175000</v>
+      </c>
+      <c r="F24" s="3">
+        <v>198000</v>
+      </c>
+      <c r="G24" s="3">
+        <v>222000</v>
+      </c>
+      <c r="H24" s="3">
+        <v>233000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>257000</v>
+      </c>
+      <c r="J24" s="3">
+        <v>262000</v>
+      </c>
+      <c r="K24" s="3">
+        <v>268000</v>
+      </c>
+      <c r="L24" s="3">
+        <v>280000</v>
+      </c>
+      <c r="M24" s="3">
+        <v>291000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>326000</v>
+      </c>
+      <c r="O24" s="3">
+        <v>350000</v>
+      </c>
+      <c r="P24" s="3">
+        <v>361000</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>373000</v>
+      </c>
+      <c r="R24" s="3">
+        <v>390000</v>
+      </c>
+      <c r="S24" s="3">
+        <v>402000</v>
+      </c>
+      <c r="T24" s="3">
+        <v>407000</v>
+      </c>
+      <c r="U24" s="3">
+        <v>414000</v>
+      </c>
+      <c r="V24" s="3">
+        <v>442000</v>
+      </c>
+      <c r="W24" s="3">
+        <v>460000</v>
+      </c>
+      <c r="X24" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>500000</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>500000</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>500000</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="3">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
+        <v>175000</v>
+      </c>
+      <c r="F25" s="3">
+        <v>198000</v>
+      </c>
+      <c r="G25" s="3">
+        <v>222000</v>
+      </c>
+      <c r="H25" s="3">
+        <v>233000</v>
+      </c>
+      <c r="I25" s="3">
+        <v>257000</v>
+      </c>
+      <c r="J25" s="3">
+        <v>262000</v>
+      </c>
+      <c r="K25" s="3">
+        <v>268000</v>
+      </c>
+      <c r="L25" s="3">
+        <v>280000</v>
+      </c>
+      <c r="M25" s="3">
+        <v>291000</v>
+      </c>
+      <c r="N25" s="3">
+        <v>326000</v>
+      </c>
+      <c r="O25" s="3">
+        <v>350000</v>
+      </c>
+      <c r="P25" s="3">
+        <v>361000</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>373000</v>
+      </c>
+      <c r="R25" s="3">
+        <v>390000</v>
+      </c>
+      <c r="S25" s="3">
+        <v>402000</v>
+      </c>
+      <c r="T25" s="3">
+        <v>407000</v>
+      </c>
+      <c r="U25" s="3">
+        <v>414000</v>
+      </c>
+      <c r="V25" s="3">
+        <v>442000</v>
+      </c>
+      <c r="W25" s="3">
+        <v>460000</v>
+      </c>
+      <c r="X25" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>500000</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>500000</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>500000</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>500000</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="3">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <v>158000</v>
+      </c>
+      <c r="F26" s="3">
+        <v>180000</v>
+      </c>
+      <c r="G26" s="3">
+        <v>202000</v>
+      </c>
+      <c r="H26" s="3">
+        <v>213000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>235000</v>
+      </c>
+      <c r="J26" s="3">
+        <v>240000</v>
+      </c>
+      <c r="K26" s="3">
+        <v>245000</v>
+      </c>
+      <c r="L26" s="3">
+        <v>257000</v>
+      </c>
+      <c r="M26" s="3">
+        <v>267000</v>
+      </c>
+      <c r="N26" s="3">
+        <v>300000</v>
+      </c>
+      <c r="O26" s="3">
+        <v>311000</v>
+      </c>
+      <c r="P26" s="3">
+        <v>321000</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>332000</v>
+      </c>
+      <c r="R26" s="3">
+        <v>348000</v>
+      </c>
+      <c r="S26" s="3">
+        <v>358000</v>
+      </c>
+      <c r="T26" s="3">
+        <v>363000</v>
+      </c>
+      <c r="U26" s="3">
+        <v>369000</v>
+      </c>
+      <c r="V26" s="3">
+        <v>395000</v>
+      </c>
+      <c r="W26" s="3">
+        <v>395000</v>
+      </c>
+      <c r="X26" s="3">
+        <v>400000</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>400000</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>400000</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>400000</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>400000</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>52000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F27" s="3">
         <v>59000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G27" s="3">
         <v>66000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H27" s="3">
         <v>69000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I27" s="3">
         <v>76000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J27" s="3">
         <v>78000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K27" s="3">
         <v>80000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L27" s="3">
         <v>84000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M27" s="3">
         <v>87000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N27" s="3">
         <v>98000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O27" s="3">
         <v>105000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P27" s="3">
         <v>108000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q27" s="3">
         <v>112000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R27" s="3">
         <v>117000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S27" s="3">
         <v>121000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T27" s="3">
         <v>122000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U27" s="3">
         <v>124000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V27" s="3">
         <v>133000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W27" s="3">
         <v>138000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X27" s="3">
         <v>151000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y27" s="3">
         <v>156000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z27" s="3">
         <v>168000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA27" s="3">
         <v>186000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB27" s="3">
         <v>204000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC27" s="3">
         <v>230000</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="2" t="s">
+    <row r="28" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B28" s="2"/>
+      <c r="C28" s="3">
         <v>124000</v>
       </c>
-      <c r="C25" s="3">
+      <c r="D28" s="3">
         <v>139000</v>
       </c>
-      <c r="D25" s="3">
+      <c r="E28" s="3">
         <v>141000</v>
       </c>
-      <c r="E25" s="3">
+      <c r="F28" s="3">
         <v>151000</v>
       </c>
-      <c r="F25" s="3">
+      <c r="G28" s="3">
         <v>161000</v>
       </c>
-      <c r="G25" s="3">
+      <c r="H28" s="3">
         <v>277000</v>
       </c>
-      <c r="H25" s="3">
+      <c r="I28" s="3">
         <v>298000</v>
       </c>
-      <c r="I25" s="3">
+      <c r="J28" s="3">
         <v>303000</v>
       </c>
-      <c r="J25" s="3">
+      <c r="K28" s="3">
         <v>308000</v>
       </c>
-      <c r="K25" s="3">
+      <c r="L28" s="3">
         <v>319000</v>
       </c>
-      <c r="L25" s="3">
+      <c r="M28" s="3">
         <v>319000</v>
       </c>
-      <c r="M25" s="3">
+      <c r="N28" s="3">
         <v>319000</v>
       </c>
-      <c r="N25" s="3">
+      <c r="O28" s="3">
         <v>319000</v>
       </c>
-      <c r="O25" s="3">
+      <c r="P28" s="3">
         <v>319000</v>
       </c>
-      <c r="P25" s="3">
+      <c r="Q28" s="3">
         <v>319000</v>
       </c>
-      <c r="Q25" s="3">
+      <c r="R28" s="3">
         <v>319000</v>
       </c>
-      <c r="R25" s="3">
+      <c r="S28" s="3">
         <v>319000</v>
       </c>
-      <c r="S25" s="3">
+      <c r="T28" s="3">
         <v>319000</v>
       </c>
-      <c r="T25" s="3">
+      <c r="U28" s="3">
         <v>319000</v>
       </c>
-      <c r="U25" s="3">
+      <c r="V28" s="3">
         <v>319000</v>
       </c>
-      <c r="V25" s="3">
+      <c r="W28" s="3">
         <v>319000</v>
       </c>
-      <c r="W25" s="3">
+      <c r="X28" s="3">
         <v>319000</v>
       </c>
-      <c r="X25" s="3">
+      <c r="Y28" s="3">
         <v>319000</v>
       </c>
-      <c r="Y25" s="3">
+      <c r="Z28" s="3">
         <v>319000</v>
       </c>
-      <c r="Z25" s="3">
+      <c r="AA28" s="3">
         <v>319000</v>
       </c>
-      <c r="AA25" s="3">
+      <c r="AB28" s="3">
         <v>319000</v>
       </c>
-      <c r="AB25" s="3">
+      <c r="AC28" s="3">
         <v>319000</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="28" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="29" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="30" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="29" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="30" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="31" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:29" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -12192,6 +12499,9 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AF0FCC-E5E6-42E5-BF86-496CDFA0D099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7815" yWindow="3975" windowWidth="26505" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7815" yWindow="3975" windowWidth="26505" windowHeight="14550" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="추가지원금" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="44">
   <si>
     <t>모델명</t>
   </si>
@@ -1048,7 +1048,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1060,6 +1060,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3723,124 +3727,126 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:W1002"/>
+  <dimension ref="A1:X1005"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.90234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="23" width="8.359375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.76171875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="24" width="8.359375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3">
+      <c r="B1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="3">
         <v>19800</v>
       </c>
-      <c r="C1" s="3">
+      <c r="D1" s="3">
         <v>26000</v>
       </c>
-      <c r="D1" s="3">
+      <c r="E1" s="3">
         <v>27830</v>
       </c>
-      <c r="E1" s="3">
+      <c r="F1" s="3">
         <v>33000</v>
       </c>
-      <c r="F1" s="3">
+      <c r="G1" s="3">
         <v>36000</v>
       </c>
-      <c r="G1" s="3">
+      <c r="H1" s="3">
         <v>39000</v>
       </c>
-      <c r="H1" s="3">
+      <c r="I1" s="3">
         <v>45000</v>
       </c>
-      <c r="I1" s="3">
+      <c r="J1" s="3">
         <v>49000</v>
       </c>
-      <c r="J1" s="3">
+      <c r="K1" s="3">
         <v>55000</v>
       </c>
-      <c r="K1" s="3">
+      <c r="L1" s="3">
         <v>59000</v>
       </c>
-      <c r="L1" s="3">
+      <c r="M1" s="3">
         <v>62000</v>
       </c>
-      <c r="M1" s="3">
+      <c r="N1" s="3">
         <v>64000</v>
       </c>
-      <c r="N1" s="3">
+      <c r="O1" s="3">
         <v>66000</v>
       </c>
-      <c r="O1" s="3">
+      <c r="P1" s="3">
         <v>68000</v>
       </c>
-      <c r="P1" s="3">
+      <c r="Q1" s="3">
         <v>69000</v>
       </c>
-      <c r="Q1" s="3">
+      <c r="R1" s="3">
         <v>79000</v>
       </c>
-      <c r="R1" s="3">
+      <c r="S1" s="3">
         <v>89000</v>
       </c>
-      <c r="S1" s="3">
+      <c r="T1" s="3">
         <v>99000</v>
       </c>
-      <c r="T1" s="3">
+      <c r="U1" s="3">
         <v>109000</v>
       </c>
-      <c r="U1" s="3">
+      <c r="V1" s="3">
         <v>119000</v>
       </c>
-      <c r="V1" s="3">
+      <c r="W1" s="3">
         <v>129000</v>
       </c>
-      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
     </row>
-    <row r="2" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="6"/>
+      <c r="C2" s="3">
         <v>150000</v>
       </c>
-      <c r="C2" s="3">
+      <c r="D2" s="3">
         <v>155000</v>
       </c>
-      <c r="D2" s="3">
+      <c r="E2" s="3">
         <v>197000</v>
       </c>
-      <c r="E2" s="3">
+      <c r="F2" s="3">
         <v>220000</v>
       </c>
-      <c r="F2" s="3">
+      <c r="G2" s="3">
         <v>245000</v>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="3">
         <v>265000</v>
       </c>
-      <c r="H2" s="3">
+      <c r="I2" s="3">
         <v>310000</v>
       </c>
-      <c r="I2" s="3">
+      <c r="J2" s="3">
         <v>333000</v>
       </c>
-      <c r="J2" s="3">
+      <c r="K2" s="3">
         <v>370000</v>
       </c>
-      <c r="K2" s="3">
+      <c r="L2" s="3">
         <v>395000</v>
       </c>
-      <c r="L2" s="3">
+      <c r="M2" s="3">
         <v>405000</v>
       </c>
-      <c r="M2" s="3">
+      <c r="N2" s="3">
         <v>410000</v>
-      </c>
-      <c r="N2" s="3">
-        <v>420000</v>
       </c>
       <c r="O2" s="3">
         <v>420000</v>
@@ -3849,67 +3855,68 @@
         <v>420000</v>
       </c>
       <c r="Q2" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R2" s="3">
         <v>453000</v>
       </c>
-      <c r="R2" s="3">
+      <c r="S2" s="3">
         <v>480000</v>
       </c>
-      <c r="S2" s="3">
+      <c r="T2" s="3">
         <v>490000</v>
       </c>
-      <c r="T2" s="3">
-        <v>500000</v>
-      </c>
       <c r="U2" s="3">
         <v>500000</v>
       </c>
       <c r="V2" s="3">
         <v>500000</v>
       </c>
-      <c r="W2" s="3"/>
+      <c r="W2" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X2" s="3"/>
     </row>
-    <row r="3" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="6"/>
+      <c r="C3" s="3">
         <v>150000</v>
       </c>
-      <c r="C3" s="3">
+      <c r="D3" s="3">
         <v>155000</v>
       </c>
-      <c r="D3" s="3">
+      <c r="E3" s="3">
         <v>197000</v>
       </c>
-      <c r="E3" s="3">
+      <c r="F3" s="3">
         <v>220000</v>
       </c>
-      <c r="F3" s="3">
+      <c r="G3" s="3">
         <v>245000</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="3">
         <v>265000</v>
       </c>
-      <c r="H3" s="3">
+      <c r="I3" s="3">
         <v>310000</v>
       </c>
-      <c r="I3" s="3">
+      <c r="J3" s="3">
         <v>333000</v>
       </c>
-      <c r="J3" s="3">
+      <c r="K3" s="3">
         <v>370000</v>
       </c>
-      <c r="K3" s="3">
+      <c r="L3" s="3">
         <v>395000</v>
       </c>
-      <c r="L3" s="3">
+      <c r="M3" s="3">
         <v>405000</v>
       </c>
-      <c r="M3" s="3">
+      <c r="N3" s="3">
         <v>410000</v>
-      </c>
-      <c r="N3" s="3">
-        <v>420000</v>
       </c>
       <c r="O3" s="3">
         <v>420000</v>
@@ -3918,67 +3925,68 @@
         <v>420000</v>
       </c>
       <c r="Q3" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R3" s="3">
         <v>453000</v>
       </c>
-      <c r="R3" s="3">
+      <c r="S3" s="3">
         <v>480000</v>
       </c>
-      <c r="S3" s="3">
+      <c r="T3" s="3">
         <v>490000</v>
       </c>
-      <c r="T3" s="3">
-        <v>500000</v>
-      </c>
       <c r="U3" s="3">
         <v>500000</v>
       </c>
       <c r="V3" s="3">
         <v>500000</v>
       </c>
-      <c r="W3" s="3"/>
+      <c r="W3" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X3" s="3"/>
     </row>
-    <row r="4" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="6"/>
+      <c r="C4" s="3">
         <v>150000</v>
       </c>
-      <c r="C4" s="3">
+      <c r="D4" s="3">
         <v>155000</v>
       </c>
-      <c r="D4" s="3">
+      <c r="E4" s="3">
         <v>197000</v>
       </c>
-      <c r="E4" s="3">
+      <c r="F4" s="3">
         <v>220000</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <v>245000</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>265000</v>
       </c>
-      <c r="H4" s="3">
+      <c r="I4" s="3">
         <v>310000</v>
       </c>
-      <c r="I4" s="3">
+      <c r="J4" s="3">
         <v>333000</v>
       </c>
-      <c r="J4" s="3">
+      <c r="K4" s="3">
         <v>370000</v>
       </c>
-      <c r="K4" s="3">
+      <c r="L4" s="3">
         <v>395000</v>
       </c>
-      <c r="L4" s="3">
+      <c r="M4" s="3">
         <v>405000</v>
       </c>
-      <c r="M4" s="3">
+      <c r="N4" s="3">
         <v>410000</v>
-      </c>
-      <c r="N4" s="3">
-        <v>420000</v>
       </c>
       <c r="O4" s="3">
         <v>420000</v>
@@ -3987,67 +3995,68 @@
         <v>420000</v>
       </c>
       <c r="Q4" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R4" s="3">
         <v>453000</v>
       </c>
-      <c r="R4" s="3">
+      <c r="S4" s="3">
         <v>480000</v>
       </c>
-      <c r="S4" s="3">
+      <c r="T4" s="3">
         <v>490000</v>
       </c>
-      <c r="T4" s="3">
-        <v>500000</v>
-      </c>
       <c r="U4" s="3">
         <v>500000</v>
       </c>
       <c r="V4" s="3">
         <v>500000</v>
       </c>
-      <c r="W4" s="3"/>
+      <c r="W4" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X4" s="3"/>
     </row>
-    <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="7"/>
+      <c r="C5" s="3">
         <v>250000</v>
       </c>
-      <c r="C5" s="3">
+      <c r="D5" s="3">
         <v>255000</v>
       </c>
-      <c r="D5" s="3">
+      <c r="E5" s="3">
         <v>297000</v>
       </c>
-      <c r="E5" s="3">
+      <c r="F5" s="3">
         <v>320000</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <v>345000</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>365000</v>
       </c>
-      <c r="H5" s="3">
+      <c r="I5" s="3">
         <v>410000</v>
       </c>
-      <c r="I5" s="3">
+      <c r="J5" s="3">
         <v>433000</v>
       </c>
-      <c r="J5" s="3">
+      <c r="K5" s="3">
         <v>470000</v>
       </c>
-      <c r="K5" s="3">
+      <c r="L5" s="3">
         <v>495000</v>
       </c>
-      <c r="L5" s="3">
+      <c r="M5" s="3">
         <v>505000</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>510000</v>
-      </c>
-      <c r="N5" s="3">
-        <v>520000</v>
       </c>
       <c r="O5" s="3">
         <v>520000</v>
@@ -4056,16 +4065,16 @@
         <v>520000</v>
       </c>
       <c r="Q5" s="3">
+        <v>520000</v>
+      </c>
+      <c r="R5" s="3">
         <v>553000</v>
       </c>
-      <c r="R5" s="3">
+      <c r="S5" s="3">
         <v>580000</v>
       </c>
-      <c r="S5" s="3">
+      <c r="T5" s="3">
         <v>590000</v>
-      </c>
-      <c r="T5" s="3">
-        <v>600000</v>
       </c>
       <c r="U5" s="3">
         <v>600000</v>
@@ -4073,50 +4082,51 @@
       <c r="V5" s="3">
         <v>600000</v>
       </c>
-      <c r="W5" s="3"/>
+      <c r="W5" s="3">
+        <v>600000</v>
+      </c>
+      <c r="X5" s="3"/>
     </row>
-    <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="7"/>
+      <c r="C6" s="3">
         <v>250000</v>
       </c>
-      <c r="C6" s="3">
+      <c r="D6" s="3">
         <v>255000</v>
       </c>
-      <c r="D6" s="3">
+      <c r="E6" s="3">
         <v>297000</v>
       </c>
-      <c r="E6" s="3">
+      <c r="F6" s="3">
         <v>320000</v>
       </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>345000</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>365000</v>
       </c>
-      <c r="H6" s="3">
+      <c r="I6" s="3">
         <v>410000</v>
       </c>
-      <c r="I6" s="3">
+      <c r="J6" s="3">
         <v>433000</v>
       </c>
-      <c r="J6" s="3">
+      <c r="K6" s="3">
         <v>470000</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="3">
         <v>495000</v>
       </c>
-      <c r="L6" s="3">
+      <c r="M6" s="3">
         <v>505000</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>510000</v>
-      </c>
-      <c r="N6" s="3">
-        <v>520000</v>
       </c>
       <c r="O6" s="3">
         <v>520000</v>
@@ -4125,16 +4135,16 @@
         <v>520000</v>
       </c>
       <c r="Q6" s="3">
+        <v>520000</v>
+      </c>
+      <c r="R6" s="3">
         <v>553000</v>
       </c>
-      <c r="R6" s="3">
+      <c r="S6" s="3">
         <v>580000</v>
       </c>
-      <c r="S6" s="3">
+      <c r="T6" s="3">
         <v>590000</v>
-      </c>
-      <c r="T6" s="3">
-        <v>600000</v>
       </c>
       <c r="U6" s="3">
         <v>600000</v>
@@ -4142,50 +4152,51 @@
       <c r="V6" s="3">
         <v>600000</v>
       </c>
-      <c r="W6" s="3"/>
+      <c r="W6" s="3">
+        <v>600000</v>
+      </c>
+      <c r="X6" s="3"/>
     </row>
-    <row r="7" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="7"/>
+      <c r="C7" s="3">
         <v>250000</v>
       </c>
-      <c r="C7" s="3">
+      <c r="D7" s="3">
         <v>255000</v>
       </c>
-      <c r="D7" s="3">
+      <c r="E7" s="3">
         <v>297000</v>
       </c>
-      <c r="E7" s="3">
+      <c r="F7" s="3">
         <v>320000</v>
       </c>
-      <c r="F7" s="3">
+      <c r="G7" s="3">
         <v>345000</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>365000</v>
       </c>
-      <c r="H7" s="3">
+      <c r="I7" s="3">
         <v>410000</v>
       </c>
-      <c r="I7" s="3">
+      <c r="J7" s="3">
         <v>433000</v>
       </c>
-      <c r="J7" s="3">
+      <c r="K7" s="3">
         <v>470000</v>
       </c>
-      <c r="K7" s="3">
+      <c r="L7" s="3">
         <v>495000</v>
       </c>
-      <c r="L7" s="3">
+      <c r="M7" s="3">
         <v>505000</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>510000</v>
-      </c>
-      <c r="N7" s="3">
-        <v>520000</v>
       </c>
       <c r="O7" s="3">
         <v>520000</v>
@@ -4194,16 +4205,16 @@
         <v>520000</v>
       </c>
       <c r="Q7" s="3">
+        <v>520000</v>
+      </c>
+      <c r="R7" s="3">
         <v>553000</v>
       </c>
-      <c r="R7" s="3">
+      <c r="S7" s="3">
         <v>580000</v>
       </c>
-      <c r="S7" s="3">
+      <c r="T7" s="3">
         <v>590000</v>
-      </c>
-      <c r="T7" s="3">
-        <v>600000</v>
       </c>
       <c r="U7" s="3">
         <v>600000</v>
@@ -4211,50 +4222,53 @@
       <c r="V7" s="3">
         <v>600000</v>
       </c>
-      <c r="W7" s="3"/>
+      <c r="W7" s="3">
+        <v>600000</v>
+      </c>
+      <c r="X7" s="3"/>
     </row>
-    <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="3">
         <v>250000</v>
       </c>
-      <c r="C8" s="3">
+      <c r="D8" s="3">
         <v>255000</v>
       </c>
-      <c r="D8" s="3">
+      <c r="E8" s="3">
         <v>297000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>320000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>345000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>365000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>410000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>433000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>470000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>495000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>505000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>510000</v>
-      </c>
-      <c r="N8" s="3">
-        <v>520000</v>
       </c>
       <c r="O8" s="3">
         <v>520000</v>
@@ -4263,16 +4277,16 @@
         <v>520000</v>
       </c>
       <c r="Q8" s="3">
+        <v>520000</v>
+      </c>
+      <c r="R8" s="3">
         <v>553000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>580000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>590000</v>
-      </c>
-      <c r="T8" s="3">
-        <v>600000</v>
       </c>
       <c r="U8" s="3">
         <v>600000</v>
@@ -4280,119 +4294,123 @@
       <c r="V8" s="3">
         <v>600000</v>
       </c>
-      <c r="W8" s="3"/>
+      <c r="W8" s="3">
+        <v>600000</v>
+      </c>
+      <c r="X8" s="3"/>
     </row>
-    <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="2"/>
+      <c r="B9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="3">
+        <v>150000</v>
+      </c>
+      <c r="D9" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>197000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G9" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H9" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>310000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>333000</v>
+      </c>
+      <c r="K9" s="3">
+        <v>370000</v>
+      </c>
+      <c r="L9" s="3">
+        <v>395000</v>
+      </c>
+      <c r="M9" s="3">
+        <v>405000</v>
+      </c>
+      <c r="N9" s="3">
+        <v>410000</v>
+      </c>
+      <c r="O9" s="3">
+        <v>420000</v>
+      </c>
+      <c r="P9" s="3">
+        <v>420000</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R9" s="3">
+        <v>453000</v>
+      </c>
+      <c r="S9" s="3">
+        <v>480000</v>
+      </c>
+      <c r="T9" s="3">
+        <v>490000</v>
+      </c>
+      <c r="U9" s="3">
+        <v>500000</v>
+      </c>
+      <c r="V9" s="3">
+        <v>500000</v>
+      </c>
+      <c r="W9" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X9" s="3"/>
+    </row>
+    <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="3">
         <v>250000</v>
       </c>
-      <c r="C9" s="3">
+      <c r="D10" s="3">
         <v>255000</v>
       </c>
-      <c r="D9" s="3">
+      <c r="E10" s="3">
         <v>297000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F10" s="3">
         <v>320000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G10" s="3">
         <v>345000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H10" s="3">
         <v>365000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I10" s="3">
         <v>410000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J10" s="3">
         <v>433000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K10" s="3">
         <v>470000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L10" s="3">
         <v>495000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M10" s="3">
         <v>505000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N10" s="3">
         <v>510000</v>
-      </c>
-      <c r="N9" s="3">
-        <v>520000</v>
-      </c>
-      <c r="O9" s="3">
-        <v>520000</v>
-      </c>
-      <c r="P9" s="3">
-        <v>520000</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>553000</v>
-      </c>
-      <c r="R9" s="3">
-        <v>580000</v>
-      </c>
-      <c r="S9" s="3">
-        <v>590000</v>
-      </c>
-      <c r="T9" s="3">
-        <v>600000</v>
-      </c>
-      <c r="U9" s="3">
-        <v>600000</v>
-      </c>
-      <c r="V9" s="3">
-        <v>600000</v>
-      </c>
-      <c r="W9" s="3"/>
-    </row>
-    <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="3">
-        <v>250000</v>
-      </c>
-      <c r="C10" s="3">
-        <v>255000</v>
-      </c>
-      <c r="D10" s="3">
-        <v>297000</v>
-      </c>
-      <c r="E10" s="3">
-        <v>320000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>345000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>365000</v>
-      </c>
-      <c r="H10" s="3">
-        <v>410000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>433000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>470000</v>
-      </c>
-      <c r="K10" s="3">
-        <v>495000</v>
-      </c>
-      <c r="L10" s="3">
-        <v>505000</v>
-      </c>
-      <c r="M10" s="3">
-        <v>510000</v>
-      </c>
-      <c r="N10" s="3">
-        <v>520000</v>
       </c>
       <c r="O10" s="3">
         <v>520000</v>
@@ -4401,16 +4419,16 @@
         <v>520000</v>
       </c>
       <c r="Q10" s="3">
+        <v>520000</v>
+      </c>
+      <c r="R10" s="3">
         <v>553000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>580000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>590000</v>
-      </c>
-      <c r="T10" s="3">
-        <v>600000</v>
       </c>
       <c r="U10" s="3">
         <v>600000</v>
@@ -4418,50 +4436,51 @@
       <c r="V10" s="3">
         <v>600000</v>
       </c>
-      <c r="W10" s="3"/>
+      <c r="W10" s="3">
+        <v>600000</v>
+      </c>
+      <c r="X10" s="3"/>
     </row>
-    <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="3">
+    <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="2"/>
+      <c r="B11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="3">
         <v>150000</v>
       </c>
-      <c r="C11" s="3">
+      <c r="D11" s="3">
         <v>155000</v>
       </c>
-      <c r="D11" s="3">
+      <c r="E11" s="3">
         <v>197000</v>
       </c>
-      <c r="E11" s="3">
+      <c r="F11" s="3">
         <v>220000</v>
       </c>
-      <c r="F11" s="3">
+      <c r="G11" s="3">
         <v>245000</v>
       </c>
-      <c r="G11" s="3">
+      <c r="H11" s="3">
         <v>265000</v>
       </c>
-      <c r="H11" s="3">
+      <c r="I11" s="3">
         <v>310000</v>
       </c>
-      <c r="I11" s="3">
+      <c r="J11" s="3">
         <v>333000</v>
       </c>
-      <c r="J11" s="3">
+      <c r="K11" s="3">
         <v>370000</v>
       </c>
-      <c r="K11" s="3">
+      <c r="L11" s="3">
         <v>395000</v>
       </c>
-      <c r="L11" s="3">
+      <c r="M11" s="3">
         <v>405000</v>
       </c>
-      <c r="M11" s="3">
+      <c r="N11" s="3">
         <v>410000</v>
-      </c>
-      <c r="N11" s="3">
-        <v>420000</v>
       </c>
       <c r="O11" s="3">
         <v>420000</v>
@@ -4470,136 +4489,140 @@
         <v>420000</v>
       </c>
       <c r="Q11" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R11" s="3">
         <v>453000</v>
       </c>
-      <c r="R11" s="3">
+      <c r="S11" s="3">
         <v>480000</v>
       </c>
-      <c r="S11" s="3">
+      <c r="T11" s="3">
         <v>490000</v>
       </c>
-      <c r="T11" s="3">
-        <v>500000</v>
-      </c>
       <c r="U11" s="3">
         <v>500000</v>
       </c>
       <c r="V11" s="3">
         <v>500000</v>
       </c>
-      <c r="W11" s="3"/>
+      <c r="W11" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X11" s="3"/>
     </row>
-    <row r="12" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="3">
+        <v>4</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="3">
+        <v>250000</v>
+      </c>
+      <c r="D12" s="3">
+        <v>255000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>297000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>320000</v>
+      </c>
+      <c r="G12" s="3">
+        <v>345000</v>
+      </c>
+      <c r="H12" s="3">
+        <v>365000</v>
+      </c>
+      <c r="I12" s="3">
+        <v>410000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>433000</v>
+      </c>
+      <c r="K12" s="3">
+        <v>470000</v>
+      </c>
+      <c r="L12" s="3">
+        <v>495000</v>
+      </c>
+      <c r="M12" s="3">
+        <v>505000</v>
+      </c>
+      <c r="N12" s="3">
+        <v>510000</v>
+      </c>
+      <c r="O12" s="3">
+        <v>520000</v>
+      </c>
+      <c r="P12" s="3">
+        <v>520000</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>520000</v>
+      </c>
+      <c r="R12" s="3">
+        <v>553000</v>
+      </c>
+      <c r="S12" s="3">
+        <v>580000</v>
+      </c>
+      <c r="T12" s="3">
+        <v>590000</v>
+      </c>
+      <c r="U12" s="3">
+        <v>600000</v>
+      </c>
+      <c r="V12" s="3">
+        <v>600000</v>
+      </c>
+      <c r="W12" s="3">
+        <v>600000</v>
+      </c>
+      <c r="X12" s="3"/>
+    </row>
+    <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="2"/>
+      <c r="B13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="3">
         <v>150000</v>
       </c>
-      <c r="C12" s="3">
+      <c r="D13" s="3">
         <v>155000</v>
       </c>
-      <c r="D12" s="3">
+      <c r="E13" s="3">
         <v>197000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F13" s="3">
         <v>220000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G13" s="3">
         <v>245000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H13" s="3">
         <v>265000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I13" s="3">
         <v>310000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J13" s="3">
         <v>333000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K13" s="3">
         <v>370000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L13" s="3">
         <v>395000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M13" s="3">
         <v>405000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N13" s="3">
         <v>410000</v>
-      </c>
-      <c r="N12" s="3">
-        <v>420000</v>
-      </c>
-      <c r="O12" s="3">
-        <v>420000</v>
-      </c>
-      <c r="P12" s="3">
-        <v>420000</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>453000</v>
-      </c>
-      <c r="R12" s="3">
-        <v>480000</v>
-      </c>
-      <c r="S12" s="3">
-        <v>490000</v>
-      </c>
-      <c r="T12" s="3">
-        <v>500000</v>
-      </c>
-      <c r="U12" s="3">
-        <v>500000</v>
-      </c>
-      <c r="V12" s="3">
-        <v>500000</v>
-      </c>
-      <c r="W12" s="3"/>
-    </row>
-    <row r="13" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="3">
-        <v>150000</v>
-      </c>
-      <c r="C13" s="3">
-        <v>155000</v>
-      </c>
-      <c r="D13" s="3">
-        <v>197000</v>
-      </c>
-      <c r="E13" s="3">
-        <v>220000</v>
-      </c>
-      <c r="F13" s="3">
-        <v>245000</v>
-      </c>
-      <c r="G13" s="3">
-        <v>265000</v>
-      </c>
-      <c r="H13" s="3">
-        <v>310000</v>
-      </c>
-      <c r="I13" s="3">
-        <v>333000</v>
-      </c>
-      <c r="J13" s="3">
-        <v>370000</v>
-      </c>
-      <c r="K13" s="3">
-        <v>395000</v>
-      </c>
-      <c r="L13" s="3">
-        <v>405000</v>
-      </c>
-      <c r="M13" s="3">
-        <v>410000</v>
-      </c>
-      <c r="N13" s="3">
-        <v>420000</v>
       </c>
       <c r="O13" s="3">
         <v>420000</v>
@@ -4608,136 +4631,138 @@
         <v>420000</v>
       </c>
       <c r="Q13" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R13" s="3">
         <v>453000</v>
       </c>
-      <c r="R13" s="3">
+      <c r="S13" s="3">
         <v>480000</v>
       </c>
-      <c r="S13" s="3">
+      <c r="T13" s="3">
         <v>490000</v>
       </c>
-      <c r="T13" s="3">
-        <v>500000</v>
-      </c>
       <c r="U13" s="3">
         <v>500000</v>
       </c>
       <c r="V13" s="3">
         <v>500000</v>
       </c>
-      <c r="W13" s="3"/>
+      <c r="W13" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X13" s="3"/>
     </row>
-    <row r="14" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="3">
-        <v>350000</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="B14" s="7"/>
       <c r="C14" s="3">
-        <v>355000</v>
+        <v>150000</v>
       </c>
       <c r="D14" s="3">
-        <v>397000</v>
+        <v>155000</v>
       </c>
       <c r="E14" s="3">
+        <v>197000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G14" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H14" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>310000</v>
+      </c>
+      <c r="J14" s="3">
+        <v>333000</v>
+      </c>
+      <c r="K14" s="3">
+        <v>370000</v>
+      </c>
+      <c r="L14" s="3">
+        <v>395000</v>
+      </c>
+      <c r="M14" s="3">
+        <v>405000</v>
+      </c>
+      <c r="N14" s="3">
+        <v>410000</v>
+      </c>
+      <c r="O14" s="3">
         <v>420000</v>
       </c>
-      <c r="F14" s="3">
-        <v>445000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>465000</v>
-      </c>
-      <c r="H14" s="3">
-        <v>510000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>533000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>570000</v>
-      </c>
-      <c r="K14" s="3">
-        <v>595000</v>
-      </c>
-      <c r="L14" s="3">
-        <v>605000</v>
-      </c>
-      <c r="M14" s="3">
-        <v>610000</v>
-      </c>
-      <c r="N14" s="3">
-        <v>620000</v>
-      </c>
-      <c r="O14" s="3">
-        <v>620000</v>
-      </c>
       <c r="P14" s="3">
-        <v>620000</v>
+        <v>420000</v>
       </c>
       <c r="Q14" s="3">
-        <v>653000</v>
+        <v>420000</v>
       </c>
       <c r="R14" s="3">
-        <v>680000</v>
+        <v>453000</v>
       </c>
       <c r="S14" s="3">
-        <v>680000</v>
+        <v>480000</v>
       </c>
       <c r="T14" s="3">
-        <v>680000</v>
+        <v>490000</v>
       </c>
       <c r="U14" s="3">
-        <v>680000</v>
+        <v>500000</v>
       </c>
       <c r="V14" s="3">
-        <v>680000</v>
-      </c>
-      <c r="W14" s="3"/>
+        <v>500000</v>
+      </c>
+      <c r="W14" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X14" s="3"/>
     </row>
-    <row r="15" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="3">
+        <v>5</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="3">
         <v>150000</v>
       </c>
-      <c r="C15" s="3">
+      <c r="D15" s="3">
         <v>155000</v>
       </c>
-      <c r="D15" s="3">
+      <c r="E15" s="3">
         <v>197000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>220000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>245000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>265000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>310000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>333000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>370000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>395000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>405000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>410000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>420000</v>
       </c>
       <c r="O15" s="3">
         <v>420000</v>
@@ -4746,67 +4771,68 @@
         <v>420000</v>
       </c>
       <c r="Q15" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R15" s="3">
         <v>453000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>480000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>490000</v>
       </c>
-      <c r="T15" s="3">
-        <v>500000</v>
-      </c>
       <c r="U15" s="3">
         <v>500000</v>
       </c>
       <c r="V15" s="3">
         <v>500000</v>
       </c>
-      <c r="W15" s="3"/>
+      <c r="W15" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X15" s="3"/>
     </row>
-    <row r="16" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="3">
+        <v>6</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="3">
         <v>150000</v>
       </c>
-      <c r="C16" s="3">
+      <c r="D16" s="3">
         <v>155000</v>
       </c>
-      <c r="D16" s="3">
+      <c r="E16" s="3">
         <v>197000</v>
       </c>
-      <c r="E16" s="3">
+      <c r="F16" s="3">
         <v>220000</v>
       </c>
-      <c r="F16" s="3">
+      <c r="G16" s="3">
         <v>245000</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>265000</v>
       </c>
-      <c r="H16" s="3">
+      <c r="I16" s="3">
         <v>310000</v>
       </c>
-      <c r="I16" s="3">
+      <c r="J16" s="3">
         <v>333000</v>
       </c>
-      <c r="J16" s="3">
+      <c r="K16" s="3">
         <v>370000</v>
       </c>
-      <c r="K16" s="3">
+      <c r="L16" s="3">
         <v>395000</v>
       </c>
-      <c r="L16" s="3">
+      <c r="M16" s="3">
         <v>405000</v>
       </c>
-      <c r="M16" s="3">
+      <c r="N16" s="3">
         <v>410000</v>
-      </c>
-      <c r="N16" s="3">
-        <v>420000</v>
       </c>
       <c r="O16" s="3">
         <v>420000</v>
@@ -4815,136 +4841,138 @@
         <v>420000</v>
       </c>
       <c r="Q16" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R16" s="3">
         <v>453000</v>
       </c>
-      <c r="R16" s="3">
+      <c r="S16" s="3">
         <v>480000</v>
       </c>
-      <c r="S16" s="3">
+      <c r="T16" s="3">
         <v>490000</v>
       </c>
-      <c r="T16" s="3">
-        <v>500000</v>
-      </c>
       <c r="U16" s="3">
         <v>500000</v>
       </c>
       <c r="V16" s="3">
         <v>500000</v>
       </c>
-      <c r="W16" s="3"/>
+      <c r="W16" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X16" s="3"/>
     </row>
-    <row r="17" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="3">
+    <row r="17" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="3">
+        <v>350000</v>
+      </c>
+      <c r="D17" s="3">
+        <v>355000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>397000</v>
+      </c>
+      <c r="F17" s="3">
+        <v>420000</v>
+      </c>
+      <c r="G17" s="3">
+        <v>445000</v>
+      </c>
+      <c r="H17" s="3">
+        <v>465000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>510000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>533000</v>
+      </c>
+      <c r="K17" s="3">
+        <v>570000</v>
+      </c>
+      <c r="L17" s="3">
+        <v>595000</v>
+      </c>
+      <c r="M17" s="3">
+        <v>605000</v>
+      </c>
+      <c r="N17" s="3">
+        <v>610000</v>
+      </c>
+      <c r="O17" s="3">
+        <v>620000</v>
+      </c>
+      <c r="P17" s="3">
+        <v>620000</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>620000</v>
+      </c>
+      <c r="R17" s="3">
+        <v>653000</v>
+      </c>
+      <c r="S17" s="3">
+        <v>680000</v>
+      </c>
+      <c r="T17" s="3">
+        <v>680000</v>
+      </c>
+      <c r="U17" s="3">
+        <v>680000</v>
+      </c>
+      <c r="V17" s="3">
+        <v>680000</v>
+      </c>
+      <c r="W17" s="3">
+        <v>680000</v>
+      </c>
+      <c r="X17" s="3"/>
+    </row>
+    <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="3">
         <v>150000</v>
       </c>
-      <c r="C17" s="3">
+      <c r="D18" s="3">
         <v>155000</v>
       </c>
-      <c r="D17" s="3">
+      <c r="E18" s="3">
         <v>197000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F18" s="3">
         <v>220000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G18" s="3">
         <v>245000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H18" s="3">
         <v>265000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I18" s="3">
         <v>310000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J18" s="3">
         <v>333000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K18" s="3">
         <v>370000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L18" s="3">
         <v>395000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M18" s="3">
         <v>405000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N18" s="3">
         <v>410000</v>
-      </c>
-      <c r="N17" s="3">
-        <v>420000</v>
-      </c>
-      <c r="O17" s="3">
-        <v>420000</v>
-      </c>
-      <c r="P17" s="3">
-        <v>420000</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>453000</v>
-      </c>
-      <c r="R17" s="3">
-        <v>480000</v>
-      </c>
-      <c r="S17" s="3">
-        <v>490000</v>
-      </c>
-      <c r="T17" s="3">
-        <v>500000</v>
-      </c>
-      <c r="U17" s="3">
-        <v>500000</v>
-      </c>
-      <c r="V17" s="3">
-        <v>500000</v>
-      </c>
-      <c r="W17" s="3"/>
-    </row>
-    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="3">
-        <v>150000</v>
-      </c>
-      <c r="C18" s="3">
-        <v>155000</v>
-      </c>
-      <c r="D18" s="3">
-        <v>197000</v>
-      </c>
-      <c r="E18" s="3">
-        <v>220000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>245000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>265000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>310000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>333000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>370000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>395000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>405000</v>
-      </c>
-      <c r="M18" s="3">
-        <v>410000</v>
-      </c>
-      <c r="N18" s="3">
-        <v>420000</v>
       </c>
       <c r="O18" s="3">
         <v>420000</v>
@@ -4953,67 +4981,68 @@
         <v>420000</v>
       </c>
       <c r="Q18" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R18" s="3">
         <v>453000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>480000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>490000</v>
       </c>
-      <c r="T18" s="3">
-        <v>500000</v>
-      </c>
       <c r="U18" s="3">
         <v>500000</v>
       </c>
       <c r="V18" s="3">
         <v>500000</v>
       </c>
-      <c r="W18" s="3"/>
+      <c r="W18" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X18" s="3"/>
     </row>
-    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="3">
+    <row r="19" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="3">
         <v>150000</v>
       </c>
-      <c r="C19" s="3">
+      <c r="D19" s="3">
         <v>155000</v>
       </c>
-      <c r="D19" s="3">
+      <c r="E19" s="3">
         <v>197000</v>
       </c>
-      <c r="E19" s="3">
+      <c r="F19" s="3">
         <v>220000</v>
       </c>
-      <c r="F19" s="3">
+      <c r="G19" s="3">
         <v>245000</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>265000</v>
       </c>
-      <c r="H19" s="3">
+      <c r="I19" s="3">
         <v>310000</v>
       </c>
-      <c r="I19" s="3">
+      <c r="J19" s="3">
         <v>333000</v>
       </c>
-      <c r="J19" s="3">
+      <c r="K19" s="3">
         <v>370000</v>
       </c>
-      <c r="K19" s="3">
+      <c r="L19" s="3">
         <v>395000</v>
       </c>
-      <c r="L19" s="3">
+      <c r="M19" s="3">
         <v>405000</v>
       </c>
-      <c r="M19" s="3">
+      <c r="N19" s="3">
         <v>410000</v>
-      </c>
-      <c r="N19" s="3">
-        <v>420000</v>
       </c>
       <c r="O19" s="3">
         <v>420000</v>
@@ -5022,67 +5051,68 @@
         <v>420000</v>
       </c>
       <c r="Q19" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R19" s="3">
         <v>453000</v>
       </c>
-      <c r="R19" s="3">
+      <c r="S19" s="3">
         <v>480000</v>
       </c>
-      <c r="S19" s="3">
+      <c r="T19" s="3">
         <v>490000</v>
       </c>
-      <c r="T19" s="3">
-        <v>500000</v>
-      </c>
       <c r="U19" s="3">
         <v>500000</v>
       </c>
       <c r="V19" s="3">
         <v>500000</v>
       </c>
-      <c r="W19" s="3"/>
+      <c r="W19" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X19" s="3"/>
     </row>
-    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="3">
+        <v>27</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="3">
         <v>150000</v>
       </c>
-      <c r="C20" s="3">
+      <c r="D20" s="3">
         <v>155000</v>
       </c>
-      <c r="D20" s="3">
+      <c r="E20" s="3">
         <v>197000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>220000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>245000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>265000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>310000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>333000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>370000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>395000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>405000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>410000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>420000</v>
       </c>
       <c r="O20" s="3">
         <v>420000</v>
@@ -5091,67 +5121,68 @@
         <v>420000</v>
       </c>
       <c r="Q20" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R20" s="3">
         <v>453000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>480000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>490000</v>
       </c>
-      <c r="T20" s="3">
-        <v>500000</v>
-      </c>
       <c r="U20" s="3">
         <v>500000</v>
       </c>
       <c r="V20" s="3">
         <v>500000</v>
       </c>
-      <c r="W20" s="3"/>
+      <c r="W20" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X20" s="3"/>
     </row>
-    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="3">
+        <v>28</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="3">
         <v>150000</v>
       </c>
-      <c r="C21" s="3">
+      <c r="D21" s="3">
         <v>155000</v>
       </c>
-      <c r="D21" s="3">
+      <c r="E21" s="3">
         <v>197000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>220000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>245000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>265000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>310000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>333000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>370000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>395000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>405000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>410000</v>
-      </c>
-      <c r="N21" s="3">
-        <v>420000</v>
       </c>
       <c r="O21" s="3">
         <v>420000</v>
@@ -5160,67 +5191,68 @@
         <v>420000</v>
       </c>
       <c r="Q21" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R21" s="3">
         <v>453000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>480000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>490000</v>
       </c>
-      <c r="T21" s="3">
-        <v>500000</v>
-      </c>
       <c r="U21" s="3">
         <v>500000</v>
       </c>
       <c r="V21" s="3">
         <v>500000</v>
       </c>
-      <c r="W21" s="3"/>
+      <c r="W21" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X21" s="3"/>
     </row>
-    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="3">
+        <v>29</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="3">
         <v>150000</v>
       </c>
-      <c r="C22" s="3">
+      <c r="D22" s="3">
         <v>155000</v>
       </c>
-      <c r="D22" s="3">
+      <c r="E22" s="3">
         <v>197000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>220000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>245000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>265000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>310000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>333000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>370000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>395000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>405000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>410000</v>
-      </c>
-      <c r="N22" s="3">
-        <v>420000</v>
       </c>
       <c r="O22" s="3">
         <v>420000</v>
@@ -5229,239 +5261,452 @@
         <v>420000</v>
       </c>
       <c r="Q22" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R22" s="3">
         <v>453000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>480000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>490000</v>
       </c>
-      <c r="T22" s="3">
-        <v>500000</v>
-      </c>
       <c r="U22" s="3">
         <v>500000</v>
       </c>
       <c r="V22" s="3">
         <v>500000</v>
       </c>
-      <c r="W22" s="3"/>
+      <c r="W22" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X22" s="3"/>
     </row>
-    <row r="23" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="3">
+        <v>150000</v>
+      </c>
+      <c r="D23" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>197000</v>
+      </c>
+      <c r="F23" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G23" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H23" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>310000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>333000</v>
+      </c>
+      <c r="K23" s="3">
+        <v>370000</v>
+      </c>
+      <c r="L23" s="3">
+        <v>395000</v>
+      </c>
+      <c r="M23" s="3">
+        <v>405000</v>
+      </c>
+      <c r="N23" s="3">
+        <v>410000</v>
+      </c>
+      <c r="O23" s="3">
+        <v>420000</v>
+      </c>
+      <c r="P23" s="3">
+        <v>420000</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R23" s="3">
+        <v>453000</v>
+      </c>
+      <c r="S23" s="3">
+        <v>480000</v>
+      </c>
+      <c r="T23" s="3">
+        <v>490000</v>
+      </c>
+      <c r="U23" s="3">
+        <v>500000</v>
+      </c>
+      <c r="V23" s="3">
+        <v>500000</v>
+      </c>
+      <c r="W23" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X23" s="3"/>
+    </row>
+    <row r="24" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="3">
+        <v>150000</v>
+      </c>
+      <c r="D24" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>197000</v>
+      </c>
+      <c r="F24" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G24" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H24" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I24" s="3">
+        <v>310000</v>
+      </c>
+      <c r="J24" s="3">
+        <v>333000</v>
+      </c>
+      <c r="K24" s="3">
+        <v>370000</v>
+      </c>
+      <c r="L24" s="3">
+        <v>395000</v>
+      </c>
+      <c r="M24" s="3">
+        <v>405000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>410000</v>
+      </c>
+      <c r="O24" s="3">
+        <v>420000</v>
+      </c>
+      <c r="P24" s="3">
+        <v>420000</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R24" s="3">
+        <v>453000</v>
+      </c>
+      <c r="S24" s="3">
+        <v>480000</v>
+      </c>
+      <c r="T24" s="3">
+        <v>490000</v>
+      </c>
+      <c r="U24" s="3">
+        <v>500000</v>
+      </c>
+      <c r="V24" s="3">
+        <v>500000</v>
+      </c>
+      <c r="W24" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X24" s="3"/>
+    </row>
+    <row r="25" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="3">
+        <v>150000</v>
+      </c>
+      <c r="D25" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E25" s="3">
+        <v>197000</v>
+      </c>
+      <c r="F25" s="3">
+        <v>220000</v>
+      </c>
+      <c r="G25" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H25" s="3">
+        <v>265000</v>
+      </c>
+      <c r="I25" s="3">
+        <v>310000</v>
+      </c>
+      <c r="J25" s="3">
+        <v>333000</v>
+      </c>
+      <c r="K25" s="3">
+        <v>370000</v>
+      </c>
+      <c r="L25" s="3">
+        <v>395000</v>
+      </c>
+      <c r="M25" s="3">
+        <v>405000</v>
+      </c>
+      <c r="N25" s="3">
+        <v>410000</v>
+      </c>
+      <c r="O25" s="3">
+        <v>420000</v>
+      </c>
+      <c r="P25" s="3">
+        <v>420000</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>420000</v>
+      </c>
+      <c r="R25" s="3">
+        <v>453000</v>
+      </c>
+      <c r="S25" s="3">
+        <v>480000</v>
+      </c>
+      <c r="T25" s="3">
+        <v>490000</v>
+      </c>
+      <c r="U25" s="3">
+        <v>500000</v>
+      </c>
+      <c r="V25" s="3">
+        <v>500000</v>
+      </c>
+      <c r="W25" s="3">
+        <v>500000</v>
+      </c>
+      <c r="X25" s="3"/>
+    </row>
+    <row r="26" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B26" s="7"/>
+      <c r="C26" s="3">
         <v>54000</v>
       </c>
-      <c r="C23" s="3">
+      <c r="D26" s="3">
         <v>55000</v>
       </c>
-      <c r="D23" s="3">
+      <c r="E26" s="3">
         <v>64000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F26" s="3">
         <v>68000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G26" s="3">
         <v>73000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H26" s="3">
         <v>78000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I26" s="3">
         <v>87000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J26" s="3">
         <v>92000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K26" s="3">
         <v>100000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L26" s="3">
         <v>105000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M26" s="3">
         <v>107000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N26" s="3">
         <v>108000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O26" s="3">
         <v>110000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P26" s="3">
         <v>110000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q26" s="3">
         <v>110000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R26" s="3">
         <v>129000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S26" s="3">
         <v>150000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T26" s="3">
         <v>154000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U26" s="3">
         <v>170000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V26" s="3">
         <v>170000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W26" s="3">
         <v>170000</v>
       </c>
-      <c r="W23" s="3"/>
+      <c r="X26" s="3"/>
     </row>
-    <row r="24" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="2" t="s">
+    <row r="27" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B27" s="7"/>
+      <c r="C27" s="3">
         <v>151000</v>
       </c>
-      <c r="C24" s="3">
+      <c r="D27" s="3">
         <v>157000</v>
       </c>
-      <c r="D24" s="3">
+      <c r="E27" s="3">
         <v>205000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F27" s="3">
         <v>230000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G27" s="3">
         <v>258000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H27" s="3">
         <v>281000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I27" s="3">
         <v>332000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J27" s="3">
         <v>357000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K27" s="3">
         <v>400000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L27" s="3">
         <v>400000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M27" s="3">
         <v>400000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N27" s="3">
         <v>400000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O27" s="3">
         <v>400000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P27" s="3">
         <v>400000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q27" s="3">
         <v>400000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R27" s="3">
         <v>400000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S27" s="3">
         <v>400000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T27" s="3">
         <v>400000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U27" s="3">
         <v>400000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V27" s="3">
         <v>400000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W27" s="3">
         <v>400000</v>
       </c>
-      <c r="W24" s="3"/>
+      <c r="X27" s="3"/>
     </row>
-    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="2" t="s">
+    <row r="28" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B28" s="7"/>
+      <c r="C28" s="3">
         <v>80000</v>
       </c>
-      <c r="C25" s="3">
+      <c r="D28" s="3">
         <v>80000</v>
       </c>
-      <c r="D25" s="3">
+      <c r="E28" s="3">
         <v>85000</v>
       </c>
-      <c r="E25" s="3">
+      <c r="F28" s="3">
         <v>88000</v>
       </c>
-      <c r="F25" s="3">
+      <c r="G28" s="3">
         <v>91000</v>
       </c>
-      <c r="G25" s="3">
+      <c r="H28" s="3">
         <v>93000</v>
       </c>
-      <c r="H25" s="3">
+      <c r="I28" s="3">
         <v>98000</v>
       </c>
-      <c r="I25" s="3">
+      <c r="J28" s="3">
         <v>101500</v>
       </c>
-      <c r="J25" s="3">
+      <c r="K28" s="3">
         <v>106000</v>
       </c>
-      <c r="K25" s="3">
+      <c r="L28" s="3">
         <v>108000</v>
       </c>
-      <c r="L25" s="3">
+      <c r="M28" s="3">
         <v>109000</v>
       </c>
-      <c r="M25" s="3">
+      <c r="N28" s="3">
         <v>110000</v>
       </c>
-      <c r="N25" s="3">
+      <c r="O28" s="3">
         <v>111000</v>
       </c>
-      <c r="O25" s="3">
+      <c r="P28" s="3">
         <v>111000</v>
       </c>
-      <c r="P25" s="3">
+      <c r="Q28" s="3">
         <v>111000</v>
       </c>
-      <c r="Q25" s="3">
+      <c r="R28" s="3">
         <v>121000</v>
       </c>
-      <c r="R25" s="3">
+      <c r="S28" s="3">
         <v>130000</v>
       </c>
-      <c r="S25" s="3">
+      <c r="T28" s="3">
         <v>130000</v>
       </c>
-      <c r="T25" s="3">
+      <c r="U28" s="3">
         <v>130000</v>
       </c>
-      <c r="U25" s="3">
+      <c r="V28" s="3">
         <v>130000</v>
       </c>
-      <c r="V25" s="3">
+      <c r="W28" s="3">
         <v>130000</v>
       </c>
-      <c r="W25" s="3"/>
+      <c r="X28" s="3"/>
     </row>
-    <row r="26" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="27" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="28" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="29" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="30" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="31" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -6432,6 +6677,9 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9069,7 +9317,7 @@
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.90234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.90234375" customWidth="1"/>
+    <col min="2" max="2" width="8.76171875" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="24" width="8.359375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="8.359375" customWidth="1"/>
     <col min="26" max="29" width="8.359375" bestFit="1" customWidth="1"/>
@@ -9079,7 +9327,7 @@
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C1" s="3">
@@ -9168,7 +9416,7 @@
       <c r="A2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="6"/>
       <c r="C2" s="3">
         <v>0</v>
       </c>
@@ -9255,7 +9503,7 @@
       <c r="A3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="4"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="3">
         <v>0</v>
       </c>
@@ -9342,7 +9590,7 @@
       <c r="A4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="3">
         <v>0</v>
       </c>
@@ -9429,7 +9677,7 @@
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="3">
         <v>0</v>
       </c>
@@ -9516,7 +9764,7 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="3">
         <v>0</v>
       </c>
@@ -9603,7 +9851,7 @@
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="3">
         <v>0</v>
       </c>
@@ -9690,7 +9938,7 @@
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="7" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="3">
@@ -9779,7 +10027,7 @@
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C9" s="3">
@@ -9868,7 +10116,7 @@
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="7" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="3">
@@ -9957,7 +10205,7 @@
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C11" s="3">
@@ -10046,7 +10294,7 @@
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="7" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="3">
@@ -10135,7 +10383,7 @@
       <c r="A13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C13" s="3">
@@ -10224,7 +10472,7 @@
       <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" s="7"/>
       <c r="C14" s="3">
         <v>0</v>
       </c>
@@ -10311,7 +10559,7 @@
       <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="7"/>
       <c r="C15" s="3">
         <v>0</v>
       </c>
@@ -10398,7 +10646,7 @@
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" s="7"/>
       <c r="C16" s="3">
         <v>0</v>
       </c>
@@ -10485,7 +10733,7 @@
       <c r="A17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="2"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="3">
         <v>0</v>
       </c>
@@ -10572,7 +10820,7 @@
       <c r="A18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="2"/>
+      <c r="B18" s="7"/>
       <c r="C18" s="3">
         <v>0</v>
       </c>
@@ -10659,7 +10907,7 @@
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="2"/>
+      <c r="B19" s="7"/>
       <c r="C19" s="3">
         <v>0</v>
       </c>
@@ -10746,7 +10994,7 @@
       <c r="A20" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="4"/>
+      <c r="B20" s="6"/>
       <c r="C20" s="3">
         <v>0</v>
       </c>
@@ -10833,7 +11081,7 @@
       <c r="A21" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="4"/>
+      <c r="B21" s="6"/>
       <c r="C21" s="3">
         <v>0</v>
       </c>
@@ -10920,7 +11168,7 @@
       <c r="A22" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="4"/>
+      <c r="B22" s="6"/>
       <c r="C22" s="3">
         <v>0</v>
       </c>
@@ -11007,7 +11255,7 @@
       <c r="A23" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="4"/>
+      <c r="B23" s="6"/>
       <c r="C23" s="3">
         <v>0</v>
       </c>
@@ -11094,7 +11342,7 @@
       <c r="A24" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="4"/>
+      <c r="B24" s="6"/>
       <c r="C24" s="3">
         <v>0</v>
       </c>
@@ -11181,7 +11429,7 @@
       <c r="A25" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="4"/>
+      <c r="B25" s="6"/>
       <c r="C25" s="3">
         <v>0</v>
       </c>
@@ -11268,7 +11516,7 @@
       <c r="A26" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="2"/>
+      <c r="B26" s="7"/>
       <c r="C26" s="3">
         <v>0</v>
       </c>
@@ -11355,7 +11603,7 @@
       <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="2"/>
+      <c r="B27" s="7"/>
       <c r="C27" s="3">
         <v>0</v>
       </c>
@@ -11442,7 +11690,7 @@
       <c r="A28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="2"/>
+      <c r="B28" s="7"/>
       <c r="C28" s="3">
         <v>124000</v>
       </c>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="44">
   <si>
     <t>모델명</t>
   </si>
@@ -4300,7 +4300,9 @@
       <c r="X8" s="3"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="B9" s="7" t="s">
         <v>43</v>
       </c>
@@ -4442,7 +4444,9 @@
       <c r="X10" s="3"/>
     </row>
     <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>3</v>
+      </c>
       <c r="B11" s="7" t="s">
         <v>43</v>
       </c>
@@ -4584,7 +4588,9 @@
       <c r="X12" s="3"/>
     </row>
     <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="B13" s="7" t="s">
         <v>43</v>
       </c>
